--- a/2022 data/excel_outputs/378_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/378_boothwise_data.xlsx
@@ -14,876 +14,1497 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="518">
   <si>
     <t>AC 378 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
+    <t>Unnamed: 22</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
     <t>POLLING STATION NAME</t>
   </si>
   <si>
-    <t>##### ### #### ;##0###ddh</t>
-  </si>
-  <si>
-    <t>####0 ##0 #### ;#0###ddh</t>
-  </si>
-  <si>
-    <t>####0 ##0 ###### ##</t>
-  </si>
-  <si>
-    <t>######## ##0 ####### ######### ; #### ##0 1ddh</t>
-  </si>
-  <si>
-    <t>######## ##0 ####### ######### ; #### ##0 2ddh</t>
-  </si>
-  <si>
-    <t>#### ###### ##### ####### #########</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ;#nn###ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ;#nn###nnddh</t>
-  </si>
-  <si>
-    <t>####0##0 ######</t>
-  </si>
-  <si>
-    <t>##### ##### ##### ###### ;##nn###ddh</t>
-  </si>
-  <si>
-    <t>##### ##### ##### ###### ;####ddh</t>
-  </si>
-  <si>
-    <t>##### ##### ##### ###### ;#nn###ddh</t>
-  </si>
-  <si>
-    <t>####0 ##0 ######</t>
-  </si>
-  <si>
-    <t>####0 ##0 ####### ######</t>
-  </si>
-  <si>
-    <t>####0 ##0 #####</t>
-  </si>
-  <si>
-    <t>####0 ##0 ###### ;##nn###ddh</t>
-  </si>
-  <si>
-    <t>####0 ##0 ###### ;#nn###ddh</t>
-  </si>
-  <si>
-    <t>####0 ##0 ####### ;##nn###ddh</t>
-  </si>
-  <si>
-    <t>####0 ##0 ####### ;#nn###ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ;#nn###nnddh</t>
-  </si>
-  <si>
-    <t>####0 ##0 #######</t>
-  </si>
-  <si>
-    <t>####0 ##0 ######### #### ####</t>
-  </si>
-  <si>
-    <t>####0 ##0 ########</t>
-  </si>
-  <si>
-    <t>####0 ##0 #### ;#########ddh ;#### ##0 .1ddh</t>
-  </si>
-  <si>
-    <t>####0 ##0 #### ;#########ddh ;#### ##0 .2ddh</t>
-  </si>
-  <si>
-    <t>###### ### ####### #####</t>
-  </si>
-  <si>
-    <t>##0##0 ##### ######### ;######ddh ;#0 ###ddh</t>
-  </si>
-  <si>
-    <t>####0 ##0 #########</t>
-  </si>
-  <si>
-    <t>##0##0 ##### ############</t>
-  </si>
-  <si>
-    <t>######## ##0 ######### ###### ;#### ##0 1ddh</t>
-  </si>
-  <si>
-    <t>######## ##0 ######### ###### ;#### ##0 2ddh</t>
-  </si>
-  <si>
-    <t>#0###0 ####0 ##0 ########</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ; ## ###ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ;### ###ddh</t>
-  </si>
-  <si>
-    <t>####0##0 #### #### ####### ;### ###ddh</t>
-  </si>
-  <si>
-    <t>####0##0 #### #### ####### ; ## ###ddh</t>
-  </si>
-  <si>
-    <t>##### ##0 ### ######### #### ##### #nn#nn.1</t>
-  </si>
-  <si>
-    <t>##### ##0 ### ######### #### ##### #nn#nn.2</t>
-  </si>
-  <si>
-    <t>####0##0 #########;#### ######ddh ;#### ##0 .1ddh</t>
-  </si>
-  <si>
-    <t>####0##0 #########;#### ######ddh ; #### ##0 .2ddh</t>
-  </si>
-  <si>
-    <t>####0##0 #######</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #####</t>
-  </si>
-  <si>
-    <t>####0##0#####</t>
-  </si>
-  <si>
-    <t>######## ##0 ####### #### ;#### ##0 1ddh</t>
-  </si>
-  <si>
-    <t>######## ##0 ####### #### ;#### ##0 2ddh</t>
-  </si>
-  <si>
-    <t>##0##0##0 ####### ##0###</t>
-  </si>
-  <si>
-    <t>##0##0##0 ####### ;#nn###ddh</t>
-  </si>
-  <si>
-    <t>#### ###### #0 ##### ######## ;#0###ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ######## #### ########## ;##nn###ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ######## #### ########## ;#nn###ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ##########</t>
-  </si>
-  <si>
-    <t>##### ##0##0 ########## ;#nn###ddh</t>
-  </si>
-  <si>
-    <t>##### ##0##0 ########## ;#nn###nnddh</t>
-  </si>
-  <si>
-    <t>##### ##0##0 #### ;#nn###ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ######## #### ;#nn###ddh</t>
-  </si>
-  <si>
-    <t>##### ##0##0 ##### ###### ;#### ##0 1ddh</t>
-  </si>
-  <si>
-    <t>##### ##0##0 ##### ###### ;#### ##0 2ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ;##nn###ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ;####ddh</t>
-  </si>
-  <si>
-    <t>##0##0 ##### ########</t>
-  </si>
-  <si>
-    <t>##### ####0##0 ##### ;########ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ########### ;##nn###ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ########### ;#nn###ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ;#### ##0 1ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ;#### ##0 2ddh</t>
-  </si>
-  <si>
-    <t>######## #### #0##0##0 ######### ##### ####</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ;#### ##0 1ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ;#### ##0 2ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ;##nn###ddh</t>
-  </si>
-  <si>
-    <t>######## ##0 #######</t>
-  </si>
-  <si>
-    <t>####0##0 #########</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ;#### ##0 1ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ;#### ##0 2ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ## #### ######</t>
-  </si>
-  <si>
-    <t>######## ##0 ####</t>
-  </si>
-  <si>
-    <t>####0##0####### ####### ;#nn###ddh</t>
-  </si>
-  <si>
-    <t>######## ##0 ####### ;#### ##0 1ddh</t>
-  </si>
-  <si>
-    <t>######## ##0 ####### ;#### ##0 2ddh</t>
-  </si>
-  <si>
-    <t>######## ##0 ##### ;#### ##0 1ddh</t>
-  </si>
-  <si>
-    <t>######## ##0 ##### ;#### ##0 2ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ####</t>
-  </si>
-  <si>
-    <t>######## ##0 ##### ;#### ##0 2 ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ########</t>
-  </si>
-  <si>
-    <t>####0##0 ######### ;######ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ######### ;#nn###ddh</t>
-  </si>
-  <si>
-    <t>######## ##0 ##########</t>
-  </si>
-  <si>
-    <t>######## ##0 #### ;#### ##0 1ddh</t>
-  </si>
-  <si>
-    <t>######## ##0 #### ;#### ##0 2ddh</t>
-  </si>
-  <si>
-    <t>######## ##0 ####### ;########ddh</t>
-  </si>
-  <si>
-    <t>######## ##0 #### ##### ####;########ddh ;#### ##0 1ddh</t>
-  </si>
-  <si>
-    <t>######## ##0 #### ##### #### ;########ddh ;#### ##0 2ddh</t>
-  </si>
-  <si>
-    <t>######## ##0 #### ##### #### ;########ddh ;#### ##0 3ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ;#nn###ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ######### ;##nn###ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ;######ddh ;#### ##0 1ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ;######ddh ;#### ##0 2ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ;######ddh</t>
-  </si>
-  <si>
-    <t>##0##0 ##### ##### ;##nn###ddh;######ddh</t>
-  </si>
-  <si>
-    <t>##0##0 ##### ##### ;#nn###ddh ;######ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ;#### ##0 1ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ;#### ##0 2ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ;#0###ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ;##0###ddh</t>
-  </si>
-  <si>
-    <t>######## ######## ##### ######## ;#### ##0 1ddh</t>
-  </si>
-  <si>
-    <t>######## ######## ##### ######## ;#### ##0 2ddh</t>
-  </si>
-  <si>
-    <t>##0##0#0 ###### ##### ######## ;##nn###ddh</t>
-  </si>
-  <si>
-    <t>##0##0#0 ###### ##### ######## ;#nn###ddh</t>
-  </si>
-  <si>
-    <t>##0##0#0 ###### ##### ######## ;####ddh</t>
-  </si>
-  <si>
-    <t>###### #### ###### ##0 ######## ;##nn###ddh</t>
-  </si>
-  <si>
-    <t>###### #### ###### ##0 ######## ;#nn###ddh</t>
-  </si>
-  <si>
-    <t>######### ####0##0 ########### ;##nn###ddh</t>
-  </si>
-  <si>
-    <t>######### ####0##0 ########### ;#nn###ddh</t>
-  </si>
-  <si>
-    <t>##0##0##### ###########;######ddh</t>
-  </si>
-  <si>
-    <t>##0##0##### ########### ;#nn###ddh</t>
-  </si>
-  <si>
-    <t>##0##0##### ########### nn;#nn###ddh</t>
-  </si>
-  <si>
-    <t>#### ##### ######## ### ### ;#nn###ddh</t>
-  </si>
-  <si>
-    <t>#### ##### ######## ########### ;######## ###ddh</t>
-  </si>
-  <si>
-    <t>##0##0#0##0##0 ########### ;#nn###ddh</t>
-  </si>
-  <si>
-    <t>##0##0#0##0##0 ########### ;#### ### ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ;#nn###ddh</t>
-  </si>
-  <si>
-    <t>##0##0##### ####### ;#nn###ddh</t>
-  </si>
-  <si>
-    <t>##0##0##### ####### ;#### ###ddh</t>
-  </si>
-  <si>
-    <t>####0##0 #######;#nn###ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ####;##nn###ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ####;#nn###ddh</t>
-  </si>
-  <si>
-    <t>####0##0#### #######</t>
-  </si>
-  <si>
-    <t>####0##0 ######### #### ######## ;#nn###ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ;#0 ###ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ;##0###ddh</t>
-  </si>
-  <si>
-    <t>#0##0 #0##0##0 #### ;## ###ddh</t>
-  </si>
-  <si>
-    <t>#0##0 #0##0##0 #### ;#### ###ddh</t>
-  </si>
-  <si>
-    <t>#0##0 #0##0##0 #### ;##0###ddh</t>
-  </si>
-  <si>
-    <t>######## ##0 ####### ;#### ##0 3ddh</t>
-  </si>
-  <si>
-    <t>######## ##0 ####### ;#### ##0 4ddh</t>
-  </si>
-  <si>
-    <t>######## ##0 ########## ####</t>
-  </si>
-  <si>
-    <t>##0##0##### ########### ;##0###ddh</t>
-  </si>
-  <si>
-    <t>##0##0##### ########### ;## ###ddh</t>
-  </si>
-  <si>
-    <t>##0##0##### ########### ;#0###ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #######</t>
-  </si>
-  <si>
-    <t>######## ##0 ###### ;#### ##0 1ddh</t>
-  </si>
-  <si>
-    <t>######## ##0 ###### ;#### ##0 2ddh</t>
-  </si>
-  <si>
-    <t>######## ##0 ###### ;#### ##0 3ddh</t>
-  </si>
-  <si>
-    <t>######## ##0 ######## ;#### ##0 1ddh</t>
-  </si>
-  <si>
-    <t>######## ##0 ######## ;#### ##0 2ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ####</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ######</t>
-  </si>
-  <si>
-    <t>######## ##0 ####### ;#### ##0 5ddh</t>
-  </si>
-  <si>
-    <t>######## ##0 ####### ;#### ##0 6ddh</t>
-  </si>
-  <si>
-    <t>##0##0##0 #0 ##### ###### ;#0###ddh</t>
-  </si>
-  <si>
-    <t>##### ######### ##### ####### ;#### ##0 1ddh</t>
-  </si>
-  <si>
-    <t>##### ######### ##### ####### ;#### ##0 2ddh</t>
-  </si>
-  <si>
-    <t>######## ####### ########</t>
-  </si>
-  <si>
-    <t>######## ##0 ######## ;#### ##0 3ddh</t>
-  </si>
-  <si>
-    <t>######## ##0 ######## ;#### ##0 4ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ### ;######ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ### ;####ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ######## #### ;#####ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ###</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ### ;#0###ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ### ;##0###ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ;##0###ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ;#0###ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ;#0###ddh</t>
-  </si>
-  <si>
-    <t>#### ####0 ##0 #########</t>
-  </si>
-  <si>
-    <t>######## ##0 ########</t>
-  </si>
-  <si>
-    <t>#### ####0 ##0 ######</t>
-  </si>
-  <si>
-    <t>####0##0 #### ;#0###ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ######</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ###</t>
-  </si>
-  <si>
-    <t>######## ##0 ###### #######</t>
-  </si>
-  <si>
-    <t>####0##0 #####</t>
-  </si>
-  <si>
-    <t>#### ####0 ##0##### ######## ;##0###ddh</t>
-  </si>
-  <si>
-    <t>#### ####0 ##0##### ######## ;#0###ddh</t>
-  </si>
-  <si>
-    <t>##### ###### #0##0##0 ##### ########</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ;#0###ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ;#0 ####ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ;##0###ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ;## ###ddh</t>
-  </si>
-  <si>
-    <t>######## ##0 ######### #### ####</t>
-  </si>
-  <si>
-    <t>####0##0 #### ;#0 ###ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ######### #### ;#0###ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ######### #### ;#### ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ######### #### ;##0###ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ;##0###ddh ;#### ##0 1ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ;#0###ddh ;#### ##0 2ddh</t>
-  </si>
-  <si>
-    <t>#### ####0 ##0 ###### ;##0###ddh</t>
-  </si>
-  <si>
-    <t>#### ####0 ##0 ###### ;#0###ddh</t>
-  </si>
-  <si>
-    <t>##0##0##### ####### ;####ddh</t>
-  </si>
-  <si>
-    <t>######## ##0 ##### ####### ;#### ##0 1ddh</t>
-  </si>
-  <si>
-    <t>######## ##0 ##### ####### ;#### ##0 2ddh</t>
-  </si>
-  <si>
-    <t>###### ### ###### ;#0###ddh</t>
-  </si>
-  <si>
-    <t>###### ### ###### ;##0###ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ####### ;#0#0.1ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ####### ;#0#0.2ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #### ;#### ##0 1ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #### ;#### ##0 2ddh</t>
-  </si>
-  <si>
-    <t>##### #0##0 ##### ;##0 ###ddh</t>
-  </si>
-  <si>
-    <t>##### #0##0 ##### ;#0 ###ddh</t>
-  </si>
-  <si>
-    <t>####0##0 #### ;#### ##0 1ddh</t>
-  </si>
-  <si>
-    <t>####0##0 #### ;#### ##0 2ddh</t>
-  </si>
-  <si>
-    <t>######## ##0 #####</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ### ####</t>
-  </si>
-  <si>
-    <t>######## ##0 ######## ;######ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #####;#0###ddh</t>
-  </si>
-  <si>
-    <t>#### ####0##0 ###### ##### ;#### #nn2ddh</t>
-  </si>
-  <si>
-    <t>#### ####0##0 ###### ##### ;#### #nn1ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ### ;##0 ddh ;##0###ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ### ;##0 ddh ;####0###ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ### ;##0 ddh ;#0###ddh</t>
-  </si>
-  <si>
-    <t>##0##0##### ###### ###;#0###ddh</t>
-  </si>
-  <si>
-    <t>##0##0##### ###### ###;####ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ### ;#0ddh ;####### ###ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ### ;#0ddh ;##nn###ddh</t>
-  </si>
-  <si>
-    <t>##### ####0##0 ###### ### ;#0#0.1ddh</t>
-  </si>
-  <si>
-    <t>##### ####0##0 ###### ### ;#0#0.2ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ;########ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ######## #####</t>
-  </si>
-  <si>
-    <t>#### #0#0####0##0 ###### ####</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #### ####### ;#### ##0 1ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #### ####### ;#### ##0 2ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ;##nn###ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ;#nn###ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ########## #### ########</t>
-  </si>
-  <si>
-    <t>######## ##0##0 ###### #### ##### ;##nn###ddh</t>
-  </si>
-  <si>
-    <t>######## ##0##0 ###### #### ##### ;#nn###ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ############</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #####</t>
-  </si>
-  <si>
-    <t>#### ####0##0 ######</t>
-  </si>
-  <si>
-    <t>#### ####0##0 #####</t>
-  </si>
-  <si>
-    <t>####0##0 ########## #### ####### ;#### ##0 1ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ########## #### ####### ;#### ##0 2ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ######### ;##0###ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ######### ;#0###ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ############ ;##0###ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ############ ;#0###ddh</t>
-  </si>
-  <si>
-    <t>#### ####0 ##0 ####### ;#0###ddh</t>
-  </si>
-  <si>
-    <t>#### ####0 ##0 ######## ;##0###ddh</t>
-  </si>
-  <si>
-    <t>#### ####0 ##0 ######## ;#0###ddh</t>
-  </si>
-  <si>
-    <t>####### ###### ####0##0 #### ;##0###ddh</t>
-  </si>
-  <si>
-    <t>####### ###### ####0##0 #### ;#0###ddh</t>
-  </si>
-  <si>
-    <t>####0##0######### ;#### ##0 1ddh</t>
-  </si>
-  <si>
-    <t>####0##0######### ;#### ##0 2ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ######## #### ########</t>
-  </si>
-  <si>
-    <t>######## ##0 ####### #### ###### ;#### ##0 1ddh</t>
-  </si>
-  <si>
-    <t>######## ##0 ####### #### ###### ;#### ##0 2ddh</t>
-  </si>
-  <si>
-    <t>######## ##0 ####### #### ###### ;#### ##0 3ddh</t>
-  </si>
-  <si>
-    <t>##### ######### ##0##0##### ######## ;#0###ddh</t>
-  </si>
-  <si>
-    <t>##### ######### ##0##0##### ######## ;####ddh</t>
-  </si>
-  <si>
-    <t>##### ######### ##0##0##### ######## ;##0###ddh</t>
-  </si>
-  <si>
-    <t>###### ### ######## ;##0###ddh</t>
-  </si>
-  <si>
-    <t>###### ### ######## ;#0###ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ;######ddh ;#0###ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ;######ddh ;####ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ;######ddh ;##0###ddh</t>
-  </si>
-  <si>
-    <t>##0##0 ##### ##0##0 ######## ;#0###ddh</t>
-  </si>
-  <si>
-    <t>##0##0 ##### ##0##0 ######## ;##0###ddh</t>
-  </si>
-  <si>
-    <t>##### ###### ####### ##### ##0##0 ##### ######## ;#0##0 1ddh</t>
-  </si>
-  <si>
-    <t>##### ###### ####### ##### ##0##0 ##### ######## ;#0##0 2ddh</t>
-  </si>
-  <si>
-    <t>##### ###### ####### ##### ##0##0 ##### ######## ;#0##0 3ddh</t>
-  </si>
-  <si>
-    <t>##### ###### ####### ##### ##0##0 ##### ######## ;#0##0 4ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ###### ##### ;#0###ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ###### ##### ;##0###ddh</t>
-  </si>
-  <si>
-    <t>######## ##0 ########## ;#### ##0 1ddh</t>
-  </si>
-  <si>
-    <t>######## ##0 ########## ;#### ##0 2ddh</t>
-  </si>
-  <si>
-    <t>######## ##0 ########## ;#### ##0 3ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ####.1 ;#### ##0 1ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ####.1 ;#### ##0 2ddh</t>
-  </si>
-  <si>
-    <t>##0##0##### ####.;#0###ddh</t>
-  </si>
-  <si>
-    <t>##0##0##### ####.;#### ###ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ####.2 ;#### ##0 1ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ####.2 ;#### ##0 2ddh</t>
-  </si>
-  <si>
-    <t>#### #0 ##### #### ;#0###ddh</t>
-  </si>
-  <si>
-    <t>### #### ##0##0 ##### ##### #### ;#0###ddh</t>
-  </si>
-  <si>
-    <t>####0##0 #### ;####ddh</t>
-  </si>
-  <si>
-    <t>### #0##0 ###### ######## ######## ;#0##0 .1ddh</t>
-  </si>
-  <si>
-    <t>### #0##0 ###### ######## ######## ;#0##0 .2ddh</t>
-  </si>
-  <si>
-    <t>### #0##0 ###### ######## ######## ;#0##0 .3ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ######### ;#### ###ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ;#0##0 .1ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ;#0##0 .2ddh</t>
-  </si>
-  <si>
-    <t>######## ##0 ####### ;#0##0 .1ddh</t>
-  </si>
-  <si>
-    <t>######## ##0 ####### ;#0##0 .2ddh</t>
-  </si>
-  <si>
-    <t>##### ##0##0##### ##### ;#0##0 .1ddh</t>
-  </si>
-  <si>
-    <t>##### ##0##0##### ##### ;#0##0 .2ddh</t>
-  </si>
-  <si>
-    <t>##### ##0##0##### ##### ;#0##0 .3ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ;#### ##0 3ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ;#### ##0 4ddh</t>
+    <t>KANYA P.P.BHALA (E.WING)</t>
+  </si>
+  <si>
+    <t>KANYA P.P.BHALA (W.WING)</t>
+  </si>
+  <si>
+    <t>P.P.KAMRAURA CHAK</t>
+  </si>
+  <si>
+    <t>J.H.SCHOOL RASULPUR HABIBULLA</t>
+  </si>
+  <si>
+    <t>SADHAN SAHAKARI SAMITI RASULPUR HABIBBULLA</t>
+  </si>
+  <si>
+    <t>P.P.HARDIYA</t>
+  </si>
+  <si>
+    <t>P.P.THANAIPUR</t>
+  </si>
+  <si>
+    <t>AD.I.COLLEGE NONAHARA (E.WING)</t>
+  </si>
+  <si>
+    <t>AD.I.COLLEGE NONAHARA (C.)</t>
+  </si>
+  <si>
+    <t>AD.I.COLLEGE NONAHARA (W.WING)</t>
+  </si>
+  <si>
+    <t>P.P.CHAKTAHA</t>
+  </si>
+  <si>
+    <t>P.P. CHAKAHLAD BADAURA</t>
+  </si>
+  <si>
+    <t>P.P. HAINSI</t>
+  </si>
+  <si>
+    <t>P.P. CHAKFARID (E.WING)</t>
+  </si>
+  <si>
+    <t>P.P. CHAKFARID (W.WING)</t>
+  </si>
+  <si>
+    <t>P.P.LAKHMIPUR (E.WING)</t>
+  </si>
+  <si>
+    <t>P.P.LAKHMIPUR (W.WING)</t>
+  </si>
+  <si>
+    <t>P.P.MALIPUR</t>
+  </si>
+  <si>
+    <t>P.P.BELPATHAR</t>
+  </si>
+  <si>
+    <t>P.P.CHAKMUKUND URF BARTAR</t>
+  </si>
+  <si>
+    <t>P.P. DHARMADIH</t>
+  </si>
+  <si>
+    <t>P.P. SAWNA(ABBASPUR) (E.WING)</t>
+  </si>
+  <si>
+    <t>P.P. SAWNA(ABBASPUR) (W.WING)</t>
+  </si>
+  <si>
+    <t>SIDHARTH PUBLIC SCHOOL LAXMI MAURYANAGAR CHAKMOLNA KHIJIR</t>
+  </si>
+  <si>
+    <t>J.H.SCHOOL UMARPUR</t>
+  </si>
+  <si>
+    <t>P.P.ARJANIPUR</t>
+  </si>
+  <si>
+    <t>P.P.DALPATPUR</t>
+  </si>
+  <si>
+    <t>J.H.SCHOOL CHAKRUKANDIPUR</t>
+  </si>
+  <si>
+    <t>P.P.HUSSEPUR KOTHIYA</t>
+  </si>
+  <si>
+    <t>R.D.MEMORIAL KANDHARPUR</t>
+  </si>
+  <si>
+    <t>A.HARI.P.P.HUSAINPUR</t>
+  </si>
+  <si>
+    <t>P.P. SHAKKARPUR (W.WING )</t>
+  </si>
+  <si>
+    <t>P.P. SHAKKARPUR (E. WING)</t>
+  </si>
+  <si>
+    <t>P.P.NAGAVA URF NAVPURA</t>
+  </si>
+  <si>
+    <t>KANYA J.H.SCHOOL SHAHABAJKULI URF SARAIYA</t>
+  </si>
+  <si>
+    <t>P.P.SHAHABAJKULI (SARAI BAHADUR)</t>
+  </si>
+  <si>
+    <t>P.P.AKBARPUR</t>
+  </si>
+  <si>
+    <t>P.P.NASIRPUR KUSUM</t>
+  </si>
+  <si>
+    <t>P.P.DARIDIH</t>
+  </si>
+  <si>
+    <t>P.P.CHAKGANI</t>
+  </si>
+  <si>
+    <t>P.P. KAMALPUR LODI (E.WING)</t>
+  </si>
+  <si>
+    <t>P.P. KAMALPUR LODI (W.WING)</t>
+  </si>
+  <si>
+    <t>P.M.V. SUKHPURA (E.WING)</t>
+  </si>
+  <si>
+    <t>P.M.V. SUKHPURA (W.WING)</t>
+  </si>
+  <si>
+    <t>H.S.SCHOOL MOHANPURA</t>
+  </si>
+  <si>
+    <t>P.P.PATKHAULI (KYAMPUR)</t>
+  </si>
+  <si>
+    <t>P.P.KYAMPUR PRATHAM</t>
+  </si>
+  <si>
+    <t>P.P.VASHDEVPUR (E.WING)</t>
+  </si>
+  <si>
+    <t>P.P.VASHDEVPUR (W.WING)</t>
+  </si>
+  <si>
+    <t>P.P.TODARPUR</t>
+  </si>
+  <si>
+    <t>P.P.MIRANPUR URF MADIYAWDIH (E.WING)</t>
+  </si>
+  <si>
+    <t>P.P.MIRANPUR URF MADIYAWDIH (W.WING)</t>
+  </si>
+  <si>
+    <t>P.P.GAUSALJAMPUR</t>
+  </si>
+  <si>
+    <t>P.P.BENSAGAR</t>
+  </si>
+  <si>
+    <t>P.P.SULTANPUR (N.WING)</t>
+  </si>
+  <si>
+    <t>P.P.SULTANPUR (S.WING.)</t>
+  </si>
+  <si>
+    <t>P.M.V.KATHAUT (N.WING)</t>
+  </si>
+  <si>
+    <t>P.M.V. KATHAUT (S.WING)</t>
+  </si>
+  <si>
+    <t>P.P. FIROJPUR KALA (N.WING)</t>
+  </si>
+  <si>
+    <t>P.P. FIROJPUR KALA (S.WING)</t>
+  </si>
+  <si>
+    <t>KANYA J.H. SCHOOL GAUSPUR</t>
+  </si>
+  <si>
+    <t>P.P. GAUSPUR (E.WING)</t>
+  </si>
+  <si>
+    <t>P.P. GAUSPUR (C)</t>
+  </si>
+  <si>
+    <t>P.P. GAUSPUR (W.WING)</t>
+  </si>
+  <si>
+    <t>J.H.SCHOOL CHAKTARAFIA</t>
+  </si>
+  <si>
+    <t>KANYA P.P.KHANDHA (HARIHARPUR)</t>
+  </si>
+  <si>
+    <t>P.P.HARIBALLAMPUR</t>
+  </si>
+  <si>
+    <t>P.P.CHAKALAM</t>
+  </si>
+  <si>
+    <t>SRI GANESH JOKHAN U.M.V.GAMBHIRPUR GOPAL CHAUBE</t>
+  </si>
+  <si>
+    <t>P.P.DAULATABAD</t>
+  </si>
+  <si>
+    <t>P.P.CHHATTARPUR</t>
+  </si>
+  <si>
+    <t>P.P.BADAIPUR</t>
+  </si>
+  <si>
+    <t>P.P.BAHADURPUR</t>
+  </si>
+  <si>
+    <t>P.P.JAKRAULI</t>
+  </si>
+  <si>
+    <t>P.P.ASMANI CHAK URF MALICHAK</t>
+  </si>
+  <si>
+    <t>P.P.TARAVA</t>
+  </si>
+  <si>
+    <t>P.V.CHAKMUKARI BAREJPUR</t>
+  </si>
+  <si>
+    <t>P.P. KESHOPUR (E.WING)</t>
+  </si>
+  <si>
+    <t>P.P. KESHOPUR (W.WING)</t>
+  </si>
+  <si>
+    <t>P.P. ICHAULI (E.WING)</t>
+  </si>
+  <si>
+    <t>P.P. ICHAULI (W.WING)</t>
+  </si>
+  <si>
+    <t>P.P. RASOOLPUR HAKIM</t>
+  </si>
+  <si>
+    <t>P.P. BAREJI (E.WING)</t>
+  </si>
+  <si>
+    <t>P.P. BAREJI (W.WING)</t>
+  </si>
+  <si>
+    <t>P.P. FAKARABAD</t>
+  </si>
+  <si>
+    <t>BABA A.H.P.P. SHAHPUR USARI</t>
+  </si>
+  <si>
+    <t>P.P. HUSSEPUR</t>
+  </si>
+  <si>
+    <t>P.P. FAJALGANJ URF PATHANPURA</t>
+  </si>
+  <si>
+    <t>P.P.NUAON (E.WING)</t>
+  </si>
+  <si>
+    <t>P.P.NUAON (W.WING)</t>
+  </si>
+  <si>
+    <t>P.P. PAIGAMBARPUR URF CHALAKPUR</t>
+  </si>
+  <si>
+    <t>P.P. JOGAPUR</t>
+  </si>
+  <si>
+    <t>P.P. SARAULI</t>
+  </si>
+  <si>
+    <t>SARVSEVA I.C. ABADAN URF BAIRAN (E.WING)</t>
+  </si>
+  <si>
+    <t>SARVSEVA I.C. ABADAN URF BAIRAN (W.WING)</t>
+  </si>
+  <si>
+    <t>P.P. BHADESAR (E.WING)</t>
+  </si>
+  <si>
+    <t>P.P. BHADESAR (W.WING)</t>
+  </si>
+  <si>
+    <t>P.P. BRAMHDASPUR</t>
+  </si>
+  <si>
+    <t>P.P. PAHADIPUR (E.WING)</t>
+  </si>
+  <si>
+    <t>P.P. PAHADIPUR (W.WING)</t>
+  </si>
+  <si>
+    <t>P.P. KARAMCHANDPUR</t>
+  </si>
+  <si>
+    <t>P.P. HATA (N.WING)</t>
+  </si>
+  <si>
+    <t>P.P. HATA (S.WING)</t>
+  </si>
+  <si>
+    <t>P.P.KARANPURA</t>
+  </si>
+  <si>
+    <t>P.P. BAKHARIPUR</t>
+  </si>
+  <si>
+    <t>P.P. BALUA THAPPA KATHAUT(HARIHARPUR) N.WING</t>
+  </si>
+  <si>
+    <t>P.P. BALUA THAPPA KATHAUT (HARIHARPUR) S.WING</t>
+  </si>
+  <si>
+    <t>P.P. ADILABAD (N.WING)</t>
+  </si>
+  <si>
+    <t>P.P. ADILABAD (S.WING)</t>
+  </si>
+  <si>
+    <t>P.P. TIWARIPUR (W.WING)</t>
+  </si>
+  <si>
+    <t>P.P. TIWARIPUR (E.WING)</t>
+  </si>
+  <si>
+    <t>P.P. BAIJALPUR</t>
+  </si>
+  <si>
+    <t>P.P. BACHCHHALPUR (SHERPUR)</t>
+  </si>
+  <si>
+    <t>P.P. SEMARA (SHERPUR)</t>
+  </si>
+  <si>
+    <t>J.H. SCHOOL SEMARA (SHERPUR) E.WING</t>
+  </si>
+  <si>
+    <t>J.H. SCHOOL SEMARA (SHERPUR) W.WING</t>
+  </si>
+  <si>
+    <t>P.P. JIYANDASPUR</t>
+  </si>
+  <si>
+    <t>P.P. AHIRAULI</t>
+  </si>
+  <si>
+    <t>P.P.NAVAPURA (N.WING)</t>
+  </si>
+  <si>
+    <t>P.P.NAVAPURA (S.WING)</t>
+  </si>
+  <si>
+    <t>KARYALAY KRISHI MANDI SAMITI YUSUFPUR (E.WING)</t>
+  </si>
+  <si>
+    <t>KARYALAY KRISHI MANDI SAMITI YUSUFPUR (W.WING)</t>
+  </si>
+  <si>
+    <t>F.H.A.NURSERY YUSUFPUR (E.WING)</t>
+  </si>
+  <si>
+    <t>F.H.A.NURSERY YUSUFPUR (W.WING)</t>
+  </si>
+  <si>
+    <t>DR.M.A. ANSARI SCHOOL YUSUFPUR (S.WING)</t>
+  </si>
+  <si>
+    <t>DR.M.A. ANSARI SCHOOL YUSUFPUR (C)</t>
+  </si>
+  <si>
+    <t>DR.M.A. ANSARI SCHOOL YUSUFPUR (N.WING))</t>
+  </si>
+  <si>
+    <t>SAHAKARI KRAY VIKRAY MU. YUSUFPUR (E.WING)</t>
+  </si>
+  <si>
+    <t>SAHAKARI KRAY VIKRAY MU. YUSUFPUR(W.WING)</t>
+  </si>
+  <si>
+    <t>ISLAMIYA P.P. MUHAMMADABAD (E.WING)</t>
+  </si>
+  <si>
+    <t>ISLAMIYA P.P. MUHAMMADABAD (W.WING)</t>
+  </si>
+  <si>
+    <t>P.P. MUHAMMADABAD (E.WING)</t>
+  </si>
+  <si>
+    <t>P.P.MUHAMMADABAD (W.EING)</t>
+  </si>
+  <si>
+    <t>J.H.SCHOOL MUHAMMADABAD (E.WING)</t>
+  </si>
+  <si>
+    <t>J.H.SCHOOL MUHAMMADABAD (W.WING)</t>
+  </si>
+  <si>
+    <t>J.H.SCHOOL MUHAMMADABAD (N.WING)</t>
+  </si>
+  <si>
+    <t>J.H.SCHOOL .MUHAMMADABAD (N.WING)</t>
+  </si>
+  <si>
+    <t>J.H.SCHOOL MUHAMMADABAD(S.WING)</t>
+  </si>
+  <si>
+    <t>KHAND VIKASH KARYALAY MOHAMMADABAD SABHA BHAWAN (S.WING)</t>
+  </si>
+  <si>
+    <t>KHAND VIKASH KARYALAY MOHAMMADABAD SABHA BHAWAN (N.WING)</t>
+  </si>
+  <si>
+    <t>KHAND VIKASH KARYALAY MOHAMMADABAD (OFFICE BHAWAN)</t>
+  </si>
+  <si>
+    <t>R.B.U.M.V. MUHAMMADABAD (N.WING)</t>
+  </si>
+  <si>
+    <t>R.B.U.M.V. MUHAMMADABAD (S.WING)</t>
+  </si>
+  <si>
+    <t>R.B.U.M.V. MUHAMMADABAD (C).</t>
+  </si>
+  <si>
+    <t>BALIKA U.P.P. DAUDPUR (W.WING)</t>
+  </si>
+  <si>
+    <t>BALIKA U.P.P. DAUDPUR (E.WING)</t>
+  </si>
+  <si>
+    <t>P.P. SALEMPUR (W.WING)</t>
+  </si>
+  <si>
+    <t>P.P. SALEMPUR (E.WING)</t>
+  </si>
+  <si>
+    <t>H.S. SCHOOL BALAPUR (N.WING)</t>
+  </si>
+  <si>
+    <t>H.S. SCHOOL BALAPUR (C.WING)</t>
+  </si>
+  <si>
+    <t>P.P. DOMANPURA</t>
+  </si>
+  <si>
+    <t>P.P. MAHARUPUR (S.WING)</t>
+  </si>
+  <si>
+    <t>P.P. MAHARUPUR (N.WING)</t>
+  </si>
+  <si>
+    <t>P.P. MURKI AGADH(E.WING)</t>
+  </si>
+  <si>
+    <t>P.P. MURKI AGADH(W.WING)</t>
+  </si>
+  <si>
+    <t>P.P.SARAI MUPHARAH</t>
+  </si>
+  <si>
+    <t>P.P.VISHUNPUR URF RAGHUBARGANJ (N.WING)</t>
+  </si>
+  <si>
+    <t>P.P.VISHUNPUR URF RAGHUBARGANJ (S.WING)</t>
+  </si>
+  <si>
+    <t>P.P.NASRATPUR</t>
+  </si>
+  <si>
+    <t>P.P.KHEMPUR</t>
+  </si>
+  <si>
+    <t>P.P.SILAICH (W.WING)</t>
+  </si>
+  <si>
+    <t>P.P.SILAICH (E.WING)</t>
+  </si>
+  <si>
+    <t>A.HI.U.M.V.PARASA (E.WING)</t>
+  </si>
+  <si>
+    <t>A.HI.U.M.V.PARASA (C.WING</t>
+  </si>
+  <si>
+    <t>A.HI.U.M.V.PARASA (C.WING)</t>
+  </si>
+  <si>
+    <t>A.HI.U.M.V.PARASA (W.WING)</t>
+  </si>
+  <si>
+    <t>P.P.GADESAR</t>
+  </si>
+  <si>
+    <t>P.P.CHAKWAKER RAJELA</t>
+  </si>
+  <si>
+    <t>P.P.KATARIYA</t>
+  </si>
+  <si>
+    <t>P.P.RAJAULI</t>
+  </si>
+  <si>
+    <t>P.V.RAYPUR</t>
+  </si>
+  <si>
+    <t>P.P.MUHAMMADPUR URF MADHOPUR</t>
+  </si>
+  <si>
+    <t>P.V.HAJIPUR</t>
+  </si>
+  <si>
+    <t>P.P.MUBARAKPUR (E.WING)</t>
+  </si>
+  <si>
+    <t>P.P.MUBARAKPUR (W.WING)</t>
+  </si>
+  <si>
+    <t>P.P.RAJAPUR (W.WING)</t>
+  </si>
+  <si>
+    <t>P.P.RAJAPUR (C.WING)</t>
+  </si>
+  <si>
+    <t>P.P.RAJAPUR (E.WING)</t>
+  </si>
+  <si>
+    <t>P.P.UTTAMPUR</t>
+  </si>
+  <si>
+    <t>P.P.FAIJULLAHPUR (E.WING)</t>
+  </si>
+  <si>
+    <t>P.P.FAIJULLAHPUR (N.WING)</t>
+  </si>
+  <si>
+    <t>P.P.MUHAMMADPUR LATIF</t>
+  </si>
+  <si>
+    <t>H.S.S.JOGAMUSAHIB (E.WING)</t>
+  </si>
+  <si>
+    <t>H.S.S.JOGAMUSAHIB (W.WING)</t>
+  </si>
+  <si>
+    <t>P.V.REDAMAR</t>
+  </si>
+  <si>
+    <t>P.V.DEWARIYA</t>
+  </si>
+  <si>
+    <t>P.V.KOTHIYA KODARTAL</t>
+  </si>
+  <si>
+    <t>P.V.SAVITAPUR</t>
+  </si>
+  <si>
+    <t>B.P.V.MUSARDEVA</t>
+  </si>
+  <si>
+    <t>B.P.V.BIRBHANPUR</t>
+  </si>
+  <si>
+    <t>B.P.P.MISHRAWALIYA</t>
+  </si>
+  <si>
+    <t>P.P.SONARI (E.WING)</t>
+  </si>
+  <si>
+    <t>P.P.SONARI (W.WING)</t>
+  </si>
+  <si>
+    <t>P.P.REWSARA</t>
+  </si>
+  <si>
+    <t>P.P.BELSADI</t>
+  </si>
+  <si>
+    <t>P.P.CHANDPUR</t>
+  </si>
+  <si>
+    <t>P.P.LAUWADIH (E.WING)</t>
+  </si>
+  <si>
+    <t>P.P.LAUWADIH (W.WING)</t>
+  </si>
+  <si>
+    <t>P.P.MALIKPURA</t>
+  </si>
+  <si>
+    <t>P.P.MALSA</t>
+  </si>
+  <si>
+    <t>P.P.MURTJIPUR</t>
+  </si>
+  <si>
+    <t>P.P.JALALPUR MUTWALI</t>
+  </si>
+  <si>
+    <t>P.P.FAKHANPUR (W.WING)</t>
+  </si>
+  <si>
+    <t>P.P.FAKHANPUR (C.WING)</t>
+  </si>
+  <si>
+    <t>P.P.FAKHANPUR (E.WING)</t>
+  </si>
+  <si>
+    <t>P.P.FAKHANPUR (S.WING)</t>
+  </si>
+  <si>
+    <t>P.P.RANIPUR (E.WING)</t>
+  </si>
+  <si>
+    <t>P.P.RANIPUR (W.WING)</t>
+  </si>
+  <si>
+    <t>H.S.SCHOOL MACHCHHATI (N.WING)</t>
+  </si>
+  <si>
+    <t>H.S.SCHOOL MACHCHHATI (S.WING)</t>
+  </si>
+  <si>
+    <t>MADARSA ISALAMIA SCHOOL MAHESHPUR</t>
+  </si>
+  <si>
+    <t>P.P.BADANPURA</t>
+  </si>
+  <si>
+    <t>P.M.V.KUNDESAR (E.WING)</t>
+  </si>
+  <si>
+    <t>P.M.V.KUNDESAR (C.WING)</t>
+  </si>
+  <si>
+    <t>P.M.V.KUNDESAR (W.WING)</t>
+  </si>
+  <si>
+    <t>P.P.CHANDANI (N.WING)</t>
+  </si>
+  <si>
+    <t>P.P.CHANDANI ( S.WING)</t>
+  </si>
+  <si>
+    <t>P.M.V.MADHUPUR (N.WING)</t>
+  </si>
+  <si>
+    <t>P.M.V.MADHUPUR (S.WING)</t>
+  </si>
+  <si>
+    <t>B.P.SURTAPUR KHAS (W.WING)</t>
+  </si>
+  <si>
+    <t>B.P.SURTAPUR KHAS (C)</t>
+  </si>
+  <si>
+    <t>B.P.SURTAPUR KHAS (E.WING)</t>
+  </si>
+  <si>
+    <t>P.P.MURKI KALAN (W.WING)</t>
+  </si>
+  <si>
+    <t>P.P.MURKI KALAN (E.WING)</t>
+  </si>
+  <si>
+    <t>P.P.TAMALPURA (E.WING)</t>
+  </si>
+  <si>
+    <t>P.P.TAMALPURA (W.WING)</t>
+  </si>
+  <si>
+    <t>B.V.MANIYA (E.WING)</t>
+  </si>
+  <si>
+    <t>B.V.MANIYA (W.WING)</t>
+  </si>
+  <si>
+    <t>P.P.BHADAURA</t>
+  </si>
+  <si>
+    <t>P.P.SUKHADEHARA (E.WING)</t>
+  </si>
+  <si>
+    <t>P.P.SUKHADEHARA (C.WING)</t>
+  </si>
+  <si>
+    <t>P.P.SUKHADEHARA (N.WING)</t>
+  </si>
+  <si>
+    <t>PURVA MADHYAMIK VIDYALAY KISHUNPURA</t>
+  </si>
+  <si>
+    <t>P.P.TETARIYA</t>
+  </si>
+  <si>
+    <t>J.H.SCHOOL BHAWARKOL</t>
+  </si>
+  <si>
+    <t>J.H.SCHOOL DAHINWAR</t>
+  </si>
+  <si>
+    <t>P.P.LOCHAIN</t>
+  </si>
+  <si>
+    <t>KANYA P.P.AMARUPUR</t>
+  </si>
+  <si>
+    <t>P.P.TARKA (N.WING)</t>
+  </si>
+  <si>
+    <t>P.P.TARKA (S.WING)</t>
+  </si>
+  <si>
+    <t>P.P.AARAJI BUDHAILA</t>
+  </si>
+  <si>
+    <t>P.P.SUKHADEHARI KALAN</t>
+  </si>
+  <si>
+    <t>B.P.V.KHAIRABARI (E.WING)</t>
+  </si>
+  <si>
+    <t>B.P.V.KHAIRABARI (W.WING)</t>
+  </si>
+  <si>
+    <t>B.P.V.MUDERA BUJURG</t>
+  </si>
+  <si>
+    <t>B.P.V.SRIPUR</t>
+  </si>
+  <si>
+    <t>P.P.BANTHA</t>
+  </si>
+  <si>
+    <t>P.P.BASANIYA</t>
+  </si>
+  <si>
+    <t>P.P.JAGDISHPUR</t>
+  </si>
+  <si>
+    <t>P.P.SURANI</t>
+  </si>
+  <si>
+    <t>J.H.SCHOOL AWATHAHI BASANT (E.WING)</t>
+  </si>
+  <si>
+    <t>J.H.SCHOOL AWATHAHI BASANT (W.WING)</t>
+  </si>
+  <si>
+    <t>PRABAL BRAMH U.M.V. AWATHAHI BASANT</t>
+  </si>
+  <si>
+    <t>P.P.MANCHA</t>
+  </si>
+  <si>
+    <t>P.P.DHUDHIYA</t>
+  </si>
+  <si>
+    <t>P.P.MASAUNI</t>
+  </si>
+  <si>
+    <t>P.P.GODAUR (W.WING)</t>
+  </si>
+  <si>
+    <t>P.P.GODAUR (W.C.)</t>
+  </si>
+  <si>
+    <t>P.P.GODAUR (W.E.)</t>
+  </si>
+  <si>
+    <t>P.P.TALKHUDIYA</t>
+  </si>
+  <si>
+    <t>P.P.SIYADI (E.WING)</t>
+  </si>
+  <si>
+    <t>P.P.SIYADI (W.WING)</t>
+  </si>
+  <si>
+    <t>P.P.SHAHPUR</t>
+  </si>
+  <si>
+    <t>P.P.GYANPUR</t>
+  </si>
+  <si>
+    <t>P.P.BALIYARIYA</t>
+  </si>
+  <si>
+    <t>P.P.KHARDIHA (E.WING)</t>
+  </si>
+  <si>
+    <t>P.P.KHARDIHA (W.WING)</t>
+  </si>
+  <si>
+    <t>P.P.BHUSAULA</t>
+  </si>
+  <si>
+    <t>P.P.MUKTAPUR URF CHARKHA</t>
+  </si>
+  <si>
+    <t>P.P.GODI (N.WING)</t>
+  </si>
+  <si>
+    <t>P.P.GODI (S.WING)</t>
+  </si>
+  <si>
+    <t>P.P. MIRJABAD ADAI (W.WING)</t>
+  </si>
+  <si>
+    <t>P.P.MIRJABAD ADAI (C)</t>
+  </si>
+  <si>
+    <t>P.P. MIRJABAD ADAI (E.WING)</t>
+  </si>
+  <si>
+    <t>P.P.MIRJABAD ADAI (E.WING)</t>
+  </si>
+  <si>
+    <t>P.P.KANUWAN (E.WING)</t>
+  </si>
+  <si>
+    <t>P.P.KANUWAN (W.WING)</t>
+  </si>
+  <si>
+    <t>P.P.MASON</t>
+  </si>
+  <si>
+    <t>J.H.SCHOOL RASULPUR (MISHANPUR)</t>
+  </si>
+  <si>
+    <t>P.V.SAJANA</t>
+  </si>
+  <si>
+    <t>P.P.LOHARPUR (E.WING)</t>
+  </si>
+  <si>
+    <t>P.P.LOHARPUR (W.WING)</t>
+  </si>
+  <si>
+    <t>P.P.PALIYA BUJURG (N.WING)</t>
+  </si>
+  <si>
+    <t>P.P.PALIYA BUJURG (S.WING)</t>
+  </si>
+  <si>
+    <t>J.H.SCHOOL FIROJPUR (E.WING)</t>
+  </si>
+  <si>
+    <t>J.H.SCHOOL FIROJPUR (W.WING)</t>
+  </si>
+  <si>
+    <t>P.P.AJAIPUR</t>
+  </si>
+  <si>
+    <t>P.P.BIRPUR (W.WING)</t>
+  </si>
+  <si>
+    <t>P.P.BIRPUR (E.WING)</t>
+  </si>
+  <si>
+    <t>PANCHAYAT BHAVAN BIRPUR (W.WING)</t>
+  </si>
+  <si>
+    <t>PANCHAYAT BHAVAN BIRPUR (E.WING)</t>
+  </si>
+  <si>
+    <t>PANCHAYAT BHAVAN BIRPUR (EXTRA KAKSH)</t>
+  </si>
+  <si>
+    <t>KANYA P.P.BIRPUR</t>
+  </si>
+  <si>
+    <t>P.P.BAHORA</t>
+  </si>
+  <si>
+    <t>P.P.BADAULI ADAI</t>
+  </si>
+  <si>
+    <t>ADARSH I.C.TARAON (E.WING)</t>
+  </si>
+  <si>
+    <t>ADARSH I.C.TARAON (W.WING)</t>
+  </si>
+  <si>
+    <t>P.P.AMLAKH</t>
+  </si>
+  <si>
+    <t>P.P.JAGAHATPUR</t>
+  </si>
+  <si>
+    <t>P.P.NIKROJPUR</t>
+  </si>
+  <si>
+    <t>P.P.KATHAR</t>
+  </si>
+  <si>
+    <t>P.P.JASDEVPUR (S.WING)</t>
+  </si>
+  <si>
+    <t>P.P.JASDEVPUR (N.WING)</t>
+  </si>
+  <si>
+    <t>P.P.JASDEVPUR (NAYA KAMARA)</t>
+  </si>
+  <si>
+    <t>P.P.NAKATIKOL</t>
+  </si>
+  <si>
+    <t>P.P.AAMGHAT</t>
+  </si>
+  <si>
+    <t>P.P.MAHESHPUR</t>
+  </si>
+  <si>
+    <t>P.P.PARSADA</t>
+  </si>
+  <si>
+    <t>P.P.DHANETHA</t>
+  </si>
+  <si>
+    <t>P.P.NARSINGHPUR KARAIL</t>
+  </si>
+  <si>
+    <t>P.P.DHARMPURA (SHERPUR)</t>
+  </si>
+  <si>
+    <t>KANYA P.P.SHERPUR KHURD (S.WING)</t>
+  </si>
+  <si>
+    <t>KANYA P.P.SHERPUR KHURD (N.WING)</t>
+  </si>
+  <si>
+    <t>UCHCHA P.V.SHERPUR KHURD (ROOM NO. 2)</t>
+  </si>
+  <si>
+    <t>UCHCHA P.V.SHERPUR KHURD (ROOM NO. 1)</t>
+  </si>
+  <si>
+    <t>P.P.SHERPUR KALAN EASTERN (E.WING)</t>
+  </si>
+  <si>
+    <t>P.P.SHERPUR KALAN EASTERN (C.WING)</t>
+  </si>
+  <si>
+    <t>P.P.SHERPUR KALAN EASTERN (W.WING)</t>
+  </si>
+  <si>
+    <t>J.H.SCHOOL SHERPUR KALAN (N.WING)</t>
+  </si>
+  <si>
+    <t>J.H.SCHOOL SHERPUR KALAN (C)</t>
+  </si>
+  <si>
+    <t>J.H.SCHOOL SHERPUR KALAN (S.WING)</t>
+  </si>
+  <si>
+    <t>P.P. SHERPUR KALA WESTERN (E.WING)</t>
+  </si>
+  <si>
+    <t>P.P. SHERPUR KALA WESTERN (W.WING)</t>
+  </si>
+  <si>
+    <t>HARIJAN P.P. SHERPUR KALA</t>
+  </si>
+  <si>
+    <t>J.H. SCHOOL PATKANIYA (N. WING)</t>
+  </si>
+  <si>
+    <t>J.H. SCHOOL PATKANIYA (S. WING)</t>
+  </si>
+  <si>
+    <t>P.P.PATKANIYA (N.WING)</t>
+  </si>
+  <si>
+    <t>P.P.PATKANIYA (S.WING)</t>
+  </si>
+  <si>
+    <t>P.P.KALYANPUR</t>
+  </si>
+  <si>
+    <t>P.P.NARAYANPUR URF HARIHARPUR</t>
+  </si>
+  <si>
+    <t>P.P. SADHOPUR U. RAMPUR (W. WING)</t>
+  </si>
+  <si>
+    <t>P.P. SADHOPUR U. RAMPUR (E. WING)</t>
+  </si>
+  <si>
+    <t>P.P. GOPALPUR</t>
+  </si>
+  <si>
+    <t>P.P.DEDHAGANWA (E. WING)</t>
+  </si>
+  <si>
+    <t>P.P.DEDHAGANWA (W. WING)</t>
+  </si>
+  <si>
+    <t>P.P. SAITBANDH</t>
+  </si>
+  <si>
+    <t>P.P. GAURA (E. WING)</t>
+  </si>
+  <si>
+    <t>P.P. GAURA (W. WING)</t>
+  </si>
+  <si>
+    <t>P.P. BADAURA</t>
+  </si>
+  <si>
+    <t>P.P. UDHARANPUR</t>
+  </si>
+  <si>
+    <t>P.P. PAKADI (E. WING)</t>
+  </si>
+  <si>
+    <t>P.P. PAKADI (W. WING)</t>
+  </si>
+  <si>
+    <t>P.P. BHUPATCHAK</t>
+  </si>
+  <si>
+    <t>P.P. TILWA (N.WING)</t>
+  </si>
+  <si>
+    <t>P.P. TILWA (S.WING)</t>
+  </si>
+  <si>
+    <t>NEHRU VIDYAPITH H.S.SCHOOL REOTIPUR (W. WING)</t>
+  </si>
+  <si>
+    <t>NEHRU VIDYAPITH H.S.SCHOOL REOTIPUR (C)</t>
+  </si>
+  <si>
+    <t>NEHRU VIDYAPITH H.S.SCHOOL REOTIPUR (E. WING)</t>
+  </si>
+  <si>
+    <t>PANCHAYAT BHAWAN REOTIPUR (E. WING)</t>
+  </si>
+  <si>
+    <t>PANCHAYAT BHAWAN REOTIPUR (W. WING)</t>
+  </si>
+  <si>
+    <t>P.P.REOTIPUR (EAST) (W. WING)</t>
+  </si>
+  <si>
+    <t>P.P.REOTIPUR (EAST) (C)</t>
+  </si>
+  <si>
+    <t>P.P.REOTIPUR (EAST) (E.WING)</t>
+  </si>
+  <si>
+    <t>P.P.REOTIPUR (EAST) (S. WING)</t>
+  </si>
+  <si>
+    <t>J.H.SCHOOL B.V. REOTIPUR (W. WING)</t>
+  </si>
+  <si>
+    <t>J.H.SCHOOL B.V. REOTIPUR (E. WING)</t>
+  </si>
+  <si>
+    <t>BLOCK SANSADHAN KENDRA ISTHIT J.H.SCHOOL REOTIPUR (R.NO. 1)</t>
+  </si>
+  <si>
+    <t>BLOCK SANSADHAN KENDRA ISTHIT J.H.SCHOOL REOTIPUR (R.NO. 2)</t>
+  </si>
+  <si>
+    <t>BLOCK SANSADHAN KENDRA ISTHIT J.H.SCHOOL REOTIPUR (R.NO. 3)</t>
+  </si>
+  <si>
+    <t>BLOCK SANSADHAN KENDRA ISTHIT J.H.SCHOOL REOTIPUR (R.NO. 4)</t>
+  </si>
+  <si>
+    <t>P.P.REOTIPUR WEST (S. WING)</t>
+  </si>
+  <si>
+    <t>P.P.REOTIPUR WEST (N. WING)</t>
+  </si>
+  <si>
+    <t>P.P.REOTIPUR WEST (E. WING)</t>
+  </si>
+  <si>
+    <t>J.H. SCHOOL TRILOKPUR (E.WING)</t>
+  </si>
+  <si>
+    <t>J.H. SCHOOL TRILOKPUR (W.WING)</t>
+  </si>
+  <si>
+    <t>P.P. NAULI-1</t>
+  </si>
+  <si>
+    <t>J.H. SCHOOL NAULI (N.WING)</t>
+  </si>
+  <si>
+    <t>J.H. SCHOOL NAULI (C)</t>
+  </si>
+  <si>
+    <t>J.H. SCHOOL NAULI (S.WING)</t>
+  </si>
+  <si>
+    <t>P.P. NAULI -II</t>
+  </si>
+  <si>
+    <t>H.S. SCHOOL NAULI (N. WING)</t>
+  </si>
+  <si>
+    <t>H.S. SCHOOL NAULI (S. WING)</t>
+  </si>
+  <si>
+    <t>AMAR SHAHID J.H.SCHOOL GAJARAHI NAULI</t>
+  </si>
+  <si>
+    <t>P.P. KHADWAL (NAULI)</t>
+  </si>
+  <si>
+    <t>LAGHU U.M.BALIKA VIDYALAY UTTRAULI (R.NO. -1)</t>
+  </si>
+  <si>
+    <t>LAGHU U.M.BALIKA VIDYALAY UTTRAULI (R.NO. -2)</t>
+  </si>
+  <si>
+    <t>LAGHU U.M.BALIKA VIDYALAY UTTRAULI (R.NO. -3)</t>
+  </si>
+  <si>
+    <t>P.P. UTTARAULI (N. WING)</t>
+  </si>
+  <si>
+    <t>P.P. UTTARAULI (S WING)</t>
+  </si>
+  <si>
+    <t>P.P. DULLAHPUR (N. WING)</t>
+  </si>
+  <si>
+    <t>P.P. DULLAHPUR (S. WING)</t>
+  </si>
+  <si>
+    <t>P.P. HASANPURA</t>
+  </si>
+  <si>
+    <t>P.P. ATHAHATHA (N. WING)</t>
+  </si>
+  <si>
+    <t>P.P. ATHAHATHA (S. WING)</t>
+  </si>
+  <si>
+    <t>P.P. NASIRPUR</t>
+  </si>
+  <si>
+    <t>J.H. SCHOOL BIRAUPUR</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA (E. WING)</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA (C)</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM NO.1 (W. WING)</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM NO.2 (E. WING)</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM NO. 396</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM NO. 397</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM NO. 398</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM NO. 399</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM NO. 400</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM NO. 401</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 402</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 403</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 404</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 405</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 406</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 407</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 408</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 409</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 410</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 411</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 412</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 413</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 414</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 415</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 416</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 417</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 418</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 419</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 420</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 421</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 422</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 423</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 424</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 425</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 426</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 427</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 428</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 429</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 430</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 431</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 432</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 433</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 434</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 435</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 436</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 437</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 438</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 439</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 440</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 441</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 442</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 443</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 444</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 445</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 446</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 447</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 448</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 449</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 450</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 451</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 452</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 453</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 454</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 455</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 456</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 457</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 458</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 459</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 460</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 461</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 462</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 463</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 464</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 465</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 466</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 467</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 468</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 469</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 470</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 471</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 472</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 473</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 474</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 475</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 476</t>
+  </si>
+  <si>
+    <t>P.P. BASUKA ROOM  (E. WING) ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 477</t>
   </si>
   <si>
     <t>TOTAL ELECTORS</t>
@@ -953,8 +1574,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -970,7 +1599,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -978,12 +1607,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1282,79 +1929,145 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:23">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:23">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>290</v>
+        <v>497</v>
       </c>
       <c r="D2" t="s">
-        <v>291</v>
+        <v>498</v>
       </c>
       <c r="E2" t="s">
-        <v>292</v>
+        <v>499</v>
       </c>
       <c r="F2" t="s">
-        <v>293</v>
+        <v>500</v>
       </c>
       <c r="G2" t="s">
-        <v>294</v>
+        <v>501</v>
       </c>
       <c r="H2" t="s">
-        <v>295</v>
+        <v>502</v>
       </c>
       <c r="I2" t="s">
-        <v>296</v>
+        <v>503</v>
       </c>
       <c r="J2" t="s">
-        <v>297</v>
+        <v>504</v>
       </c>
       <c r="K2" t="s">
-        <v>298</v>
+        <v>505</v>
       </c>
       <c r="L2" t="s">
-        <v>299</v>
+        <v>506</v>
       </c>
       <c r="M2" t="s">
-        <v>300</v>
+        <v>507</v>
       </c>
       <c r="N2" t="s">
-        <v>301</v>
+        <v>508</v>
       </c>
       <c r="O2" t="s">
-        <v>302</v>
+        <v>509</v>
       </c>
       <c r="P2" t="s">
-        <v>303</v>
+        <v>510</v>
       </c>
       <c r="Q2" t="s">
-        <v>304</v>
+        <v>511</v>
       </c>
       <c r="R2" t="s">
-        <v>305</v>
+        <v>512</v>
       </c>
       <c r="S2" t="s">
-        <v>306</v>
+        <v>513</v>
       </c>
       <c r="T2" t="s">
-        <v>307</v>
+        <v>514</v>
       </c>
       <c r="U2" t="s">
-        <v>308</v>
+        <v>515</v>
       </c>
       <c r="V2" t="s">
-        <v>309</v>
+        <v>516</v>
       </c>
       <c r="W2" t="s">
-        <v>310</v>
+        <v>517</v>
       </c>
     </row>
     <row r="3" spans="1:23">
@@ -1362,7 +2075,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C3">
         <v>938</v>
@@ -1433,7 +2146,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C4">
         <v>863</v>
@@ -1504,7 +2217,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="C5">
         <v>580</v>
@@ -1575,7 +2288,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="C6">
         <v>828</v>
@@ -1646,7 +2359,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="C7">
         <v>886</v>
@@ -1717,7 +2430,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="C8">
         <v>513</v>
@@ -1788,7 +2501,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C9">
         <v>808</v>
@@ -1859,7 +2572,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="C10">
         <v>795</v>
@@ -1930,7 +2643,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C11">
         <v>807</v>
@@ -2001,7 +2714,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="C12">
         <v>1136</v>
@@ -2072,7 +2785,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C13">
         <v>1027</v>
@@ -2143,7 +2856,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="C14">
         <v>1049</v>
@@ -2214,7 +2927,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C15">
         <v>1160</v>
@@ -2285,7 +2998,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="C16">
         <v>495</v>
@@ -2356,7 +3069,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C17">
         <v>616</v>
@@ -2427,7 +3140,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="C18">
         <v>1175</v>
@@ -2498,7 +3211,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="C19">
         <v>1143</v>
@@ -2569,7 +3282,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="C20">
         <v>1064</v>
@@ -2640,7 +3353,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="C21">
         <v>1063</v>
@@ -2711,7 +3424,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="C22">
         <v>811</v>
@@ -2782,7 +3495,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="C23">
         <v>946</v>
@@ -2853,7 +3566,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="C24">
         <v>743</v>
@@ -2924,7 +3637,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="C25">
         <v>589</v>
@@ -2995,7 +3708,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="C26">
         <v>870</v>
@@ -3066,7 +3779,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="C27">
         <v>724</v>
@@ -3137,7 +3850,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="C28">
         <v>863</v>
@@ -3208,7 +3921,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="C29">
         <v>765</v>
@@ -3279,7 +3992,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="C30">
         <v>912</v>
@@ -3350,7 +4063,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="C31">
         <v>688</v>
@@ -3421,7 +4134,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="C32">
         <v>1209</v>
@@ -3492,7 +4205,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="C33">
         <v>768</v>
@@ -3563,7 +4276,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="C34">
         <v>908</v>
@@ -3634,7 +4347,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="C35">
         <v>523</v>
@@ -3705,7 +4418,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="C36">
         <v>801</v>
@@ -3776,7 +4489,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="C37">
         <v>757</v>
@@ -3847,7 +4560,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="C38">
         <v>968</v>
@@ -3918,7 +4631,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="C39">
         <v>848</v>
@@ -3989,7 +4702,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="C40">
         <v>734</v>
@@ -4060,7 +4773,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="C41">
         <v>647</v>
@@ -4131,7 +4844,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="C42">
         <v>738</v>
@@ -4202,7 +4915,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="C43">
         <v>681</v>
@@ -4273,7 +4986,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="C44">
         <v>734</v>
@@ -4344,7 +5057,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="C45">
         <v>709</v>
@@ -4415,7 +5128,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="C46">
         <v>578</v>
@@ -4486,7 +5199,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="C47">
         <v>534</v>
@@ -4557,7 +5270,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="C48">
         <v>641</v>
@@ -4628,7 +5341,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="C49">
         <v>948</v>
@@ -4699,7 +5412,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="C50">
         <v>1151</v>
@@ -4770,7 +5483,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="C51">
         <v>950</v>
@@ -4841,7 +5554,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="C52">
         <v>971</v>
@@ -4912,7 +5625,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="C53">
         <v>1155</v>
@@ -4983,7 +5696,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="C54">
         <v>752</v>
@@ -5054,7 +5767,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="C55">
         <v>900</v>
@@ -5125,7 +5838,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="C56">
         <v>929</v>
@@ -5196,7 +5909,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="C57">
         <v>1115</v>
@@ -5267,7 +5980,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="C58">
         <v>737</v>
@@ -5338,7 +6051,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="C59">
         <v>719</v>
@@ -5409,7 +6122,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>54</v>
+        <v>81</v>
       </c>
       <c r="C60">
         <v>1097</v>
@@ -5480,7 +6193,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="C61">
         <v>401</v>
@@ -5551,7 +6264,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="C62">
         <v>1084</v>
@@ -5622,7 +6335,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="C63">
         <v>995</v>
@@ -5693,7 +6406,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="C64">
         <v>632</v>
@@ -5764,7 +6477,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>57</v>
+        <v>86</v>
       </c>
       <c r="C65">
         <v>1187</v>
@@ -5835,7 +6548,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="C66">
         <v>809</v>
@@ -5906,7 +6619,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="C67">
         <v>729</v>
@@ -5977,7 +6690,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="C68">
         <v>653</v>
@@ -6048,7 +6761,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="C69">
         <v>1078</v>
@@ -6119,7 +6832,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="C70">
         <v>1233</v>
@@ -6190,7 +6903,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>9</v>
+        <v>92</v>
       </c>
       <c r="C71">
         <v>963</v>
@@ -6261,7 +6974,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>9</v>
+        <v>93</v>
       </c>
       <c r="C72">
         <v>994</v>
@@ -6332,7 +7045,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C73">
         <v>692</v>
@@ -6403,7 +7116,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="C74">
         <v>388</v>
@@ -6474,7 +7187,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="C75">
         <v>676</v>
@@ -6545,7 +7258,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>65</v>
+        <v>97</v>
       </c>
       <c r="C76">
         <v>631</v>
@@ -6616,7 +7329,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="C77">
         <v>923</v>
@@ -6687,7 +7400,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="C78">
         <v>599</v>
@@ -6758,7 +7471,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="C79">
         <v>524</v>
@@ -6829,7 +7542,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>69</v>
+        <v>101</v>
       </c>
       <c r="C80">
         <v>779</v>
@@ -6900,7 +7613,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="C81">
         <v>873</v>
@@ -6971,7 +7684,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="C82">
         <v>1135</v>
@@ -7042,7 +7755,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>72</v>
+        <v>104</v>
       </c>
       <c r="C83">
         <v>884</v>
@@ -7113,7 +7826,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="C84">
         <v>603</v>
@@ -7184,7 +7897,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="C85">
         <v>881</v>
@@ -7255,7 +7968,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>75</v>
+        <v>107</v>
       </c>
       <c r="C86">
         <v>711</v>
@@ -7326,7 +8039,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="C87">
         <v>762</v>
@@ -7397,7 +8110,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="C88">
         <v>865</v>
@@ -7468,7 +8181,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="C89">
         <v>852</v>
@@ -7539,7 +8252,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="C90">
         <v>1049</v>
@@ -7610,7 +8323,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="C91">
         <v>554</v>
@@ -7681,7 +8394,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="C92">
         <v>961</v>
@@ -7752,7 +8465,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>82</v>
+        <v>114</v>
       </c>
       <c r="C93">
         <v>759</v>
@@ -7823,7 +8536,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>83</v>
+        <v>115</v>
       </c>
       <c r="C94">
         <v>842</v>
@@ -7894,7 +8607,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="C95">
         <v>831</v>
@@ -7965,7 +8678,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>84</v>
+        <v>117</v>
       </c>
       <c r="C96">
         <v>729</v>
@@ -8036,7 +8749,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="C97">
         <v>830</v>
@@ -8107,7 +8820,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>86</v>
+        <v>119</v>
       </c>
       <c r="C98">
         <v>981</v>
@@ -8178,7 +8891,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>87</v>
+        <v>120</v>
       </c>
       <c r="C99">
         <v>751</v>
@@ -8249,7 +8962,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="C100">
         <v>748</v>
@@ -8320,7 +9033,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>89</v>
+        <v>122</v>
       </c>
       <c r="C101">
         <v>959</v>
@@ -8391,7 +9104,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>90</v>
+        <v>123</v>
       </c>
       <c r="C102">
         <v>974</v>
@@ -8462,7 +9175,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>91</v>
+        <v>124</v>
       </c>
       <c r="C103">
         <v>1191</v>
@@ -8533,7 +9246,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>69</v>
+        <v>125</v>
       </c>
       <c r="C104">
         <v>812</v>
@@ -8604,7 +9317,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>70</v>
+        <v>126</v>
       </c>
       <c r="C105">
         <v>556</v>
@@ -8675,7 +9388,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>92</v>
+        <v>127</v>
       </c>
       <c r="C106">
         <v>1082</v>
@@ -8746,7 +9459,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>93</v>
+        <v>128</v>
       </c>
       <c r="C107">
         <v>1036</v>
@@ -8817,7 +9530,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>94</v>
+        <v>129</v>
       </c>
       <c r="C108">
         <v>1053</v>
@@ -8888,7 +9601,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="C109">
         <v>1183</v>
@@ -8959,7 +9672,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>95</v>
+        <v>131</v>
       </c>
       <c r="C110">
         <v>888</v>
@@ -9030,7 +9743,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>87</v>
+        <v>132</v>
       </c>
       <c r="C111">
         <v>910</v>
@@ -9101,7 +9814,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>96</v>
+        <v>133</v>
       </c>
       <c r="C112">
         <v>1008</v>
@@ -9172,7 +9885,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>96</v>
+        <v>134</v>
       </c>
       <c r="C113">
         <v>890</v>
@@ -9243,7 +9956,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>43</v>
+        <v>135</v>
       </c>
       <c r="C114">
         <v>843</v>
@@ -9314,7 +10027,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="C115">
         <v>797</v>
@@ -9385,7 +10098,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C116">
         <v>644</v>
@@ -9456,7 +10169,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="C117">
         <v>983</v>
@@ -9527,7 +10240,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="C118">
         <v>1168</v>
@@ -9598,7 +10311,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="C119">
         <v>929</v>
@@ -9669,7 +10382,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>53</v>
+        <v>141</v>
       </c>
       <c r="C120">
         <v>781</v>
@@ -9740,7 +10453,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>102</v>
+        <v>142</v>
       </c>
       <c r="C121">
         <v>1074</v>
@@ -9811,7 +10524,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>103</v>
+        <v>143</v>
       </c>
       <c r="C122">
         <v>619</v>
@@ -9882,7 +10595,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>104</v>
+        <v>144</v>
       </c>
       <c r="C123">
         <v>898</v>
@@ -9953,7 +10666,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>105</v>
+        <v>145</v>
       </c>
       <c r="C124">
         <v>880</v>
@@ -10024,7 +10737,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>106</v>
+        <v>146</v>
       </c>
       <c r="C125">
         <v>919</v>
@@ -10095,7 +10808,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>107</v>
+        <v>147</v>
       </c>
       <c r="C126">
         <v>933</v>
@@ -10166,7 +10879,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>108</v>
+        <v>148</v>
       </c>
       <c r="C127">
         <v>1174</v>
@@ -10237,7 +10950,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>109</v>
+        <v>149</v>
       </c>
       <c r="C128">
         <v>761</v>
@@ -10308,7 +11021,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="C129">
         <v>1083</v>
@@ -10379,7 +11092,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>109</v>
+        <v>151</v>
       </c>
       <c r="C130">
         <v>966</v>
@@ -10450,7 +11163,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>109</v>
+        <v>152</v>
       </c>
       <c r="C131">
         <v>855</v>
@@ -10521,7 +11234,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>110</v>
+        <v>153</v>
       </c>
       <c r="C132">
         <v>806</v>
@@ -10592,7 +11305,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>110</v>
+        <v>154</v>
       </c>
       <c r="C133">
         <v>1189</v>
@@ -10663,7 +11376,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>109</v>
+        <v>155</v>
       </c>
       <c r="C134">
         <v>1175</v>
@@ -10734,7 +11447,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>111</v>
+        <v>156</v>
       </c>
       <c r="C135">
         <v>1050</v>
@@ -10805,7 +11518,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>112</v>
+        <v>157</v>
       </c>
       <c r="C136">
         <v>779</v>
@@ -10876,7 +11589,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>113</v>
+        <v>158</v>
       </c>
       <c r="C137">
         <v>1242</v>
@@ -10947,7 +11660,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>114</v>
+        <v>159</v>
       </c>
       <c r="C138">
         <v>670</v>
@@ -11018,7 +11731,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>64</v>
+        <v>160</v>
       </c>
       <c r="C139">
         <v>1005</v>
@@ -11089,7 +11802,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>65</v>
+        <v>161</v>
       </c>
       <c r="C140">
         <v>1129</v>
@@ -11160,7 +11873,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>115</v>
+        <v>162</v>
       </c>
       <c r="C141">
         <v>1044</v>
@@ -11231,7 +11944,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>116</v>
+        <v>163</v>
       </c>
       <c r="C142">
         <v>993</v>
@@ -11302,7 +12015,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>116</v>
+        <v>164</v>
       </c>
       <c r="C143">
         <v>1071</v>
@@ -11373,7 +12086,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>117</v>
+        <v>165</v>
       </c>
       <c r="C144">
         <v>1077</v>
@@ -11444,7 +12157,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>116</v>
+        <v>166</v>
       </c>
       <c r="C145">
         <v>1169</v>
@@ -11515,7 +12228,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>118</v>
+        <v>167</v>
       </c>
       <c r="C146">
         <v>1047</v>
@@ -11586,7 +12299,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>118</v>
+        <v>168</v>
       </c>
       <c r="C147">
         <v>832</v>
@@ -11657,7 +12370,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>119</v>
+        <v>169</v>
       </c>
       <c r="C148">
         <v>1027</v>
@@ -11728,7 +12441,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="C149">
         <v>1190</v>
@@ -11799,7 +12512,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>120</v>
+        <v>171</v>
       </c>
       <c r="C150">
         <v>1042</v>
@@ -11870,7 +12583,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>121</v>
+        <v>172</v>
       </c>
       <c r="C151">
         <v>1075</v>
@@ -11941,7 +12654,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>79</v>
+        <v>173</v>
       </c>
       <c r="C152">
         <v>965</v>
@@ -12012,7 +12725,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>80</v>
+        <v>174</v>
       </c>
       <c r="C153">
         <v>1095</v>
@@ -12083,7 +12796,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>122</v>
+        <v>175</v>
       </c>
       <c r="C154">
         <v>1223</v>
@@ -12154,7 +12867,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>71</v>
+        <v>176</v>
       </c>
       <c r="C155">
         <v>526</v>
@@ -12225,7 +12938,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>71</v>
+        <v>177</v>
       </c>
       <c r="C156">
         <v>764</v>
@@ -12296,7 +13009,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>123</v>
+        <v>178</v>
       </c>
       <c r="C157">
         <v>1198</v>
@@ -12367,7 +13080,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>124</v>
+        <v>179</v>
       </c>
       <c r="C158">
         <v>992</v>
@@ -12438,7 +13151,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>124</v>
+        <v>180</v>
       </c>
       <c r="C159">
         <v>611</v>
@@ -12509,7 +13222,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>69</v>
+        <v>181</v>
       </c>
       <c r="C160">
         <v>827</v>
@@ -12580,7 +13293,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>70</v>
+        <v>182</v>
       </c>
       <c r="C161">
         <v>993</v>
@@ -12651,7 +13364,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>122</v>
+        <v>183</v>
       </c>
       <c r="C162">
         <v>752</v>
@@ -12722,7 +13435,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>122</v>
+        <v>184</v>
       </c>
       <c r="C163">
         <v>689</v>
@@ -12793,7 +13506,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>125</v>
+        <v>185</v>
       </c>
       <c r="C164">
         <v>1129</v>
@@ -12864,7 +13577,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>126</v>
+        <v>186</v>
       </c>
       <c r="C165">
         <v>762</v>
@@ -12935,7 +13648,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>127</v>
+        <v>187</v>
       </c>
       <c r="C166">
         <v>1034</v>
@@ -13006,7 +13719,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>128</v>
+        <v>188</v>
       </c>
       <c r="C167">
         <v>449</v>
@@ -13077,7 +13790,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>129</v>
+        <v>189</v>
       </c>
       <c r="C168">
         <v>769</v>
@@ -13148,7 +13861,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>129</v>
+        <v>190</v>
       </c>
       <c r="C169">
         <v>686</v>
@@ -13219,7 +13932,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>129</v>
+        <v>191</v>
       </c>
       <c r="C170">
         <v>1135</v>
@@ -13290,7 +14003,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>43</v>
+        <v>192</v>
       </c>
       <c r="C171">
         <v>647</v>
@@ -13361,7 +14074,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>11</v>
+        <v>193</v>
       </c>
       <c r="C172">
         <v>598</v>
@@ -13432,7 +14145,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>130</v>
+        <v>194</v>
       </c>
       <c r="C173">
         <v>1081</v>
@@ -13503,7 +14216,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>131</v>
+        <v>195</v>
       </c>
       <c r="C174">
         <v>1156</v>
@@ -13574,7 +14287,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>132</v>
+        <v>196</v>
       </c>
       <c r="C175">
         <v>900</v>
@@ -13645,7 +14358,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>133</v>
+        <v>197</v>
       </c>
       <c r="C176">
         <v>949</v>
@@ -13716,7 +14429,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>133</v>
+        <v>198</v>
       </c>
       <c r="C177">
         <v>1046</v>
@@ -13787,7 +14500,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>133</v>
+        <v>199</v>
       </c>
       <c r="C178">
         <v>1063</v>
@@ -13858,7 +14571,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>134</v>
+        <v>200</v>
       </c>
       <c r="C179">
         <v>1163</v>
@@ -13929,7 +14642,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>79</v>
+        <v>201</v>
       </c>
       <c r="C180">
         <v>934</v>
@@ -14000,7 +14713,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>80</v>
+        <v>202</v>
       </c>
       <c r="C181">
         <v>797</v>
@@ -14071,7 +14784,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>135</v>
+        <v>203</v>
       </c>
       <c r="C182">
         <v>886</v>
@@ -14142,7 +14855,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>136</v>
+        <v>204</v>
       </c>
       <c r="C183">
         <v>1092</v>
@@ -14213,7 +14926,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>85</v>
+        <v>205</v>
       </c>
       <c r="C184">
         <v>810</v>
@@ -14284,7 +14997,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>137</v>
+        <v>206</v>
       </c>
       <c r="C185">
         <v>591</v>
@@ -14355,7 +15068,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>138</v>
+        <v>207</v>
       </c>
       <c r="C186">
         <v>953</v>
@@ -14426,7 +15139,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>139</v>
+        <v>208</v>
       </c>
       <c r="C187">
         <v>840</v>
@@ -14497,7 +15210,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>140</v>
+        <v>209</v>
       </c>
       <c r="C188">
         <v>952</v>
@@ -14568,7 +15281,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>11</v>
+        <v>210</v>
       </c>
       <c r="C189">
         <v>917</v>
@@ -14639,7 +15352,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>102</v>
+        <v>211</v>
       </c>
       <c r="C190">
         <v>827</v>
@@ -14710,7 +15423,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>103</v>
+        <v>212</v>
       </c>
       <c r="C191">
         <v>552</v>
@@ -14781,7 +15494,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>141</v>
+        <v>213</v>
       </c>
       <c r="C192">
         <v>737</v>
@@ -14852,7 +15565,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>85</v>
+        <v>214</v>
       </c>
       <c r="C193">
         <v>453</v>
@@ -14923,7 +15636,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>85</v>
+        <v>215</v>
       </c>
       <c r="C194">
         <v>781</v>
@@ -14994,7 +15707,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>73</v>
+        <v>216</v>
       </c>
       <c r="C195">
         <v>778</v>
@@ -15065,7 +15778,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>53</v>
+        <v>217</v>
       </c>
       <c r="C196">
         <v>447</v>
@@ -15136,7 +15849,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>142</v>
+        <v>218</v>
       </c>
       <c r="C197">
         <v>768</v>
@@ -15207,7 +15920,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>143</v>
+        <v>219</v>
       </c>
       <c r="C198">
         <v>627</v>
@@ -15278,7 +15991,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>144</v>
+        <v>220</v>
       </c>
       <c r="C199">
         <v>1185</v>
@@ -15349,7 +16062,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>74</v>
+        <v>221</v>
       </c>
       <c r="C200">
         <v>705</v>
@@ -15420,7 +16133,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>75</v>
+        <v>222</v>
       </c>
       <c r="C201">
         <v>637</v>
@@ -15491,7 +16204,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>74</v>
+        <v>223</v>
       </c>
       <c r="C202">
         <v>664</v>
@@ -15562,7 +16275,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>75</v>
+        <v>224</v>
       </c>
       <c r="C203">
         <v>747</v>
@@ -15633,7 +16346,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>72</v>
+        <v>225</v>
       </c>
       <c r="C204">
         <v>904</v>
@@ -15704,7 +16417,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>102</v>
+        <v>226</v>
       </c>
       <c r="C205">
         <v>871</v>
@@ -15775,7 +16488,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>103</v>
+        <v>227</v>
       </c>
       <c r="C206">
         <v>760</v>
@@ -15846,7 +16559,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>145</v>
+        <v>228</v>
       </c>
       <c r="C207">
         <v>685</v>
@@ -15917,7 +16630,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>146</v>
+        <v>229</v>
       </c>
       <c r="C208">
         <v>678</v>
@@ -15988,7 +16701,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>147</v>
+        <v>230</v>
       </c>
       <c r="C209">
         <v>879</v>
@@ -16059,7 +16772,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>88</v>
+        <v>228</v>
       </c>
       <c r="C210">
         <v>1196</v>
@@ -16130,7 +16843,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>148</v>
+        <v>231</v>
       </c>
       <c r="C211">
         <v>753</v>
@@ -16201,7 +16914,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>79</v>
+        <v>232</v>
       </c>
       <c r="C212">
         <v>1050</v>
@@ -16272,7 +16985,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>80</v>
+        <v>233</v>
       </c>
       <c r="C213">
         <v>1010</v>
@@ -16343,7 +17056,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>135</v>
+        <v>234</v>
       </c>
       <c r="C214">
         <v>866</v>
@@ -16414,7 +17127,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>136</v>
+        <v>235</v>
       </c>
       <c r="C215">
         <v>1170</v>
@@ -16485,7 +17198,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>149</v>
+        <v>236</v>
       </c>
       <c r="C216">
         <v>1047</v>
@@ -16556,7 +17269,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>150</v>
+        <v>237</v>
       </c>
       <c r="C217">
         <v>838</v>
@@ -16627,7 +17340,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>102</v>
+        <v>238</v>
       </c>
       <c r="C218">
         <v>826</v>
@@ -16698,7 +17411,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>103</v>
+        <v>239</v>
       </c>
       <c r="C219">
         <v>876</v>
@@ -16769,7 +17482,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>151</v>
+        <v>240</v>
       </c>
       <c r="C220">
         <v>1189</v>
@@ -16840,7 +17553,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>151</v>
+        <v>241</v>
       </c>
       <c r="C221">
         <v>1193</v>
@@ -16911,7 +17624,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>152</v>
+        <v>242</v>
       </c>
       <c r="C222">
         <v>709</v>
@@ -16982,7 +17695,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>153</v>
+        <v>243</v>
       </c>
       <c r="C223">
         <v>653</v>
@@ -17053,7 +17766,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>154</v>
+        <v>244</v>
       </c>
       <c r="C224">
         <v>997</v>
@@ -17124,7 +17837,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>145</v>
+        <v>245</v>
       </c>
       <c r="C225">
         <v>1001</v>
@@ -17195,7 +17908,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>146</v>
+        <v>246</v>
       </c>
       <c r="C226">
         <v>984</v>
@@ -17266,7 +17979,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>155</v>
+        <v>247</v>
       </c>
       <c r="C227">
         <v>1044</v>
@@ -17337,7 +18050,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>156</v>
+        <v>248</v>
       </c>
       <c r="C228">
         <v>967</v>
@@ -17408,7 +18121,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>142</v>
+        <v>249</v>
       </c>
       <c r="C229">
         <v>907</v>
@@ -17479,7 +18192,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>143</v>
+        <v>250</v>
       </c>
       <c r="C230">
         <v>972</v>
@@ -17550,7 +18263,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>79</v>
+        <v>251</v>
       </c>
       <c r="C231">
         <v>830</v>
@@ -17621,7 +18334,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>80</v>
+        <v>252</v>
       </c>
       <c r="C232">
         <v>866</v>
@@ -17692,7 +18405,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>157</v>
+        <v>253</v>
       </c>
       <c r="C233">
         <v>964</v>
@@ -17763,7 +18476,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>158</v>
+        <v>254</v>
       </c>
       <c r="C234">
         <v>932</v>
@@ -17834,7 +18547,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>158</v>
+        <v>255</v>
       </c>
       <c r="C235">
         <v>900</v>
@@ -17905,7 +18618,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>159</v>
+        <v>256</v>
       </c>
       <c r="C236">
         <v>506</v>
@@ -17976,7 +18689,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>160</v>
+        <v>257</v>
       </c>
       <c r="C237">
         <v>589</v>
@@ -18047,7 +18760,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>161</v>
+        <v>258</v>
       </c>
       <c r="C238">
         <v>990</v>
@@ -18118,7 +18831,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>162</v>
+        <v>259</v>
       </c>
       <c r="C239">
         <v>789</v>
@@ -18189,7 +18902,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>161</v>
+        <v>260</v>
       </c>
       <c r="C240">
         <v>640</v>
@@ -18260,7 +18973,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>105</v>
+        <v>261</v>
       </c>
       <c r="C241">
         <v>1020</v>
@@ -18331,7 +19044,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>104</v>
+        <v>262</v>
       </c>
       <c r="C242">
         <v>1038</v>
@@ -18402,7 +19115,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>104</v>
+        <v>263</v>
       </c>
       <c r="C243">
         <v>594</v>
@@ -18473,7 +19186,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>163</v>
+        <v>264</v>
       </c>
       <c r="C244">
         <v>1098</v>
@@ -18544,7 +19257,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>164</v>
+        <v>265</v>
       </c>
       <c r="C245">
         <v>1166</v>
@@ -18615,7 +19328,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>66</v>
+        <v>266</v>
       </c>
       <c r="C246">
         <v>502</v>
@@ -18686,7 +19399,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>67</v>
+        <v>267</v>
       </c>
       <c r="C247">
         <v>1097</v>
@@ -18757,7 +19470,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>165</v>
+        <v>268</v>
       </c>
       <c r="C248">
         <v>1168</v>
@@ -18828,7 +19541,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>165</v>
+        <v>269</v>
       </c>
       <c r="C249">
         <v>1061</v>
@@ -18899,7 +19612,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>131</v>
+        <v>270</v>
       </c>
       <c r="C250">
         <v>680</v>
@@ -18970,7 +19683,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>131</v>
+        <v>271</v>
       </c>
       <c r="C251">
         <v>681</v>
@@ -19041,7 +19754,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>166</v>
+        <v>272</v>
       </c>
       <c r="C252">
         <v>915</v>
@@ -19112,7 +19825,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>43</v>
+        <v>273</v>
       </c>
       <c r="C253">
         <v>675</v>
@@ -19183,7 +19896,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>167</v>
+        <v>274</v>
       </c>
       <c r="C254">
         <v>775</v>
@@ -19254,7 +19967,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>168</v>
+        <v>275</v>
       </c>
       <c r="C255">
         <v>1120</v>
@@ -19325,7 +20038,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>74</v>
+        <v>276</v>
       </c>
       <c r="C256">
         <v>666</v>
@@ -19396,7 +20109,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>75</v>
+        <v>277</v>
       </c>
       <c r="C257">
         <v>581</v>
@@ -19467,7 +20180,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>43</v>
+        <v>278</v>
       </c>
       <c r="C258">
         <v>915</v>
@@ -19538,7 +20251,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>169</v>
+        <v>279</v>
       </c>
       <c r="C259">
         <v>738</v>
@@ -19609,7 +20322,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>169</v>
+        <v>280</v>
       </c>
       <c r="C260">
         <v>863</v>
@@ -19680,7 +20393,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>170</v>
+        <v>281</v>
       </c>
       <c r="C261">
         <v>507</v>
@@ -19751,7 +20464,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>171</v>
+        <v>282</v>
       </c>
       <c r="C262">
         <v>913</v>
@@ -19822,7 +20535,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>131</v>
+        <v>283</v>
       </c>
       <c r="C263">
         <v>890</v>
@@ -19893,7 +20606,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>165</v>
+        <v>284</v>
       </c>
       <c r="C264">
         <v>585</v>
@@ -19964,7 +20677,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>172</v>
+        <v>285</v>
       </c>
       <c r="C265">
         <v>800</v>
@@ -20035,7 +20748,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>43</v>
+        <v>286</v>
       </c>
       <c r="C266">
         <v>696</v>
@@ -20106,7 +20819,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>173</v>
+        <v>287</v>
       </c>
       <c r="C267">
         <v>904</v>
@@ -20177,7 +20890,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>11</v>
+        <v>288</v>
       </c>
       <c r="C268">
         <v>861</v>
@@ -20248,7 +20961,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>167</v>
+        <v>289</v>
       </c>
       <c r="C269">
         <v>976</v>
@@ -20319,7 +21032,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>173</v>
+        <v>290</v>
       </c>
       <c r="C270">
         <v>744</v>
@@ -20390,7 +21103,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>174</v>
+        <v>291</v>
       </c>
       <c r="C271">
         <v>1074</v>
@@ -20461,7 +21174,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>175</v>
+        <v>292</v>
       </c>
       <c r="C272">
         <v>943</v>
@@ -20532,7 +21245,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>175</v>
+        <v>293</v>
       </c>
       <c r="C273">
         <v>1030</v>
@@ -20603,7 +21316,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>176</v>
+        <v>294</v>
       </c>
       <c r="C274">
         <v>825</v>
@@ -20674,7 +21387,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>66</v>
+        <v>295</v>
       </c>
       <c r="C275">
         <v>718</v>
@@ -20745,7 +21458,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>67</v>
+        <v>296</v>
       </c>
       <c r="C276">
         <v>714</v>
@@ -20816,7 +21529,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>74</v>
+        <v>297</v>
       </c>
       <c r="C277">
         <v>649</v>
@@ -20887,7 +21600,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>75</v>
+        <v>298</v>
       </c>
       <c r="C278">
         <v>711</v>
@@ -20958,7 +21671,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>173</v>
+        <v>299</v>
       </c>
       <c r="C279">
         <v>982</v>
@@ -21029,7 +21742,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>177</v>
+        <v>300</v>
       </c>
       <c r="C280">
         <v>1138</v>
@@ -21100,7 +21813,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>178</v>
+        <v>301</v>
       </c>
       <c r="C281">
         <v>1033</v>
@@ -21171,7 +21884,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>179</v>
+        <v>302</v>
       </c>
       <c r="C282">
         <v>1099</v>
@@ -21242,7 +21955,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>73</v>
+        <v>303</v>
       </c>
       <c r="C283">
         <v>939</v>
@@ -21313,7 +22026,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>180</v>
+        <v>304</v>
       </c>
       <c r="C284">
         <v>998</v>
@@ -21384,7 +22097,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>164</v>
+        <v>305</v>
       </c>
       <c r="C285">
         <v>716</v>
@@ -21455,7 +22168,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>142</v>
+        <v>306</v>
       </c>
       <c r="C286">
         <v>643</v>
@@ -21526,7 +22239,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>143</v>
+        <v>307</v>
       </c>
       <c r="C287">
         <v>654</v>
@@ -21597,7 +22310,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>85</v>
+        <v>308</v>
       </c>
       <c r="C288">
         <v>1088</v>
@@ -21668,7 +22381,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>85</v>
+        <v>309</v>
       </c>
       <c r="C289">
         <v>509</v>
@@ -21739,7 +22452,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>163</v>
+        <v>310</v>
       </c>
       <c r="C290">
         <v>962</v>
@@ -21810,7 +22523,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>164</v>
+        <v>311</v>
       </c>
       <c r="C291">
         <v>974</v>
@@ -21881,7 +22594,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>11</v>
+        <v>312</v>
       </c>
       <c r="C292">
         <v>561</v>
@@ -21952,7 +22665,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>181</v>
+        <v>313</v>
       </c>
       <c r="C293">
         <v>644</v>
@@ -22023,7 +22736,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>182</v>
+        <v>314</v>
       </c>
       <c r="C294">
         <v>906</v>
@@ -22094,7 +22807,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>182</v>
+        <v>315</v>
       </c>
       <c r="C295">
         <v>745</v>
@@ -22165,7 +22878,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>183</v>
+        <v>316</v>
       </c>
       <c r="C296">
         <v>848</v>
@@ -22236,7 +22949,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>184</v>
+        <v>317</v>
       </c>
       <c r="C297">
         <v>1054</v>
@@ -22307,7 +23020,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>185</v>
+        <v>318</v>
       </c>
       <c r="C298">
         <v>1000</v>
@@ -22378,7 +23091,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>185</v>
+        <v>319</v>
       </c>
       <c r="C299">
         <v>1234</v>
@@ -22449,7 +23162,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>186</v>
+        <v>320</v>
       </c>
       <c r="C300">
         <v>753</v>
@@ -22520,7 +23233,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>187</v>
+        <v>321</v>
       </c>
       <c r="C301">
         <v>692</v>
@@ -22591,7 +23304,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>188</v>
+        <v>322</v>
       </c>
       <c r="C302">
         <v>886</v>
@@ -22662,7 +23375,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>189</v>
+        <v>323</v>
       </c>
       <c r="C303">
         <v>686</v>
@@ -22733,7 +23446,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>89</v>
+        <v>324</v>
       </c>
       <c r="C304">
         <v>851</v>
@@ -22804,7 +23517,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>90</v>
+        <v>325</v>
       </c>
       <c r="C305">
         <v>746</v>
@@ -22875,7 +23588,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="C306">
         <v>619</v>
@@ -22946,7 +23659,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>147</v>
+        <v>327</v>
       </c>
       <c r="C307">
         <v>853</v>
@@ -23017,7 +23730,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>145</v>
+        <v>328</v>
       </c>
       <c r="C308">
         <v>1140</v>
@@ -23088,7 +23801,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>146</v>
+        <v>329</v>
       </c>
       <c r="C309">
         <v>882</v>
@@ -23159,7 +23872,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>191</v>
+        <v>330</v>
       </c>
       <c r="C310">
         <v>1035</v>
@@ -23230,7 +23943,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>192</v>
+        <v>331</v>
       </c>
       <c r="C311">
         <v>1010</v>
@@ -23301,7 +24014,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>145</v>
+        <v>332</v>
       </c>
       <c r="C312">
         <v>1121</v>
@@ -23372,7 +24085,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>146</v>
+        <v>333</v>
       </c>
       <c r="C313">
         <v>1094</v>
@@ -23443,7 +24156,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>11</v>
+        <v>334</v>
       </c>
       <c r="C314">
         <v>566</v>
@@ -23514,7 +24227,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>163</v>
+        <v>335</v>
       </c>
       <c r="C315">
         <v>842</v>
@@ -23585,7 +24298,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>164</v>
+        <v>336</v>
       </c>
       <c r="C316">
         <v>945</v>
@@ -23656,7 +24369,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>164</v>
+        <v>337</v>
       </c>
       <c r="C317">
         <v>902</v>
@@ -23727,7 +24440,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>193</v>
+        <v>338</v>
       </c>
       <c r="C318">
         <v>1152</v>
@@ -23798,7 +24511,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>194</v>
+        <v>339</v>
       </c>
       <c r="C319">
         <v>1029</v>
@@ -23869,7 +24582,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>195</v>
+        <v>340</v>
       </c>
       <c r="C320">
         <v>985</v>
@@ -23940,7 +24653,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>196</v>
+        <v>341</v>
       </c>
       <c r="C321">
         <v>1028</v>
@@ -24011,7 +24724,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>173</v>
+        <v>342</v>
       </c>
       <c r="C322">
         <v>678</v>
@@ -24082,7 +24795,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>197</v>
+        <v>343</v>
       </c>
       <c r="C323">
         <v>748</v>
@@ -24153,7 +24866,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>198</v>
+        <v>344</v>
       </c>
       <c r="C324">
         <v>760</v>
@@ -24224,7 +24937,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>199</v>
+        <v>345</v>
       </c>
       <c r="C325">
         <v>1066</v>
@@ -24295,7 +25008,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>200</v>
+        <v>346</v>
       </c>
       <c r="C326">
         <v>1025</v>
@@ -24366,7 +25079,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>200</v>
+        <v>347</v>
       </c>
       <c r="C327">
         <v>1098</v>
@@ -24437,7 +25150,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>173</v>
+        <v>348</v>
       </c>
       <c r="C328">
         <v>699</v>
@@ -24508,7 +25221,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>43</v>
+        <v>349</v>
       </c>
       <c r="C329">
         <v>534</v>
@@ -24579,7 +25292,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>73</v>
+        <v>350</v>
       </c>
       <c r="C330">
         <v>952</v>
@@ -24650,7 +25363,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>201</v>
+        <v>351</v>
       </c>
       <c r="C331">
         <v>768</v>
@@ -24721,7 +25434,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>202</v>
+        <v>352</v>
       </c>
       <c r="C332">
         <v>730</v>
@@ -24792,7 +25505,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>145</v>
+        <v>353</v>
       </c>
       <c r="C333">
         <v>1059</v>
@@ -24863,7 +25576,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>146</v>
+        <v>354</v>
       </c>
       <c r="C334">
         <v>1079</v>
@@ -24934,7 +25647,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>155</v>
+        <v>355</v>
       </c>
       <c r="C335">
         <v>1019</v>
@@ -25005,7 +25718,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>43</v>
+        <v>356</v>
       </c>
       <c r="C336">
         <v>670</v>
@@ -25076,7 +25789,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>173</v>
+        <v>357</v>
       </c>
       <c r="C337">
         <v>597</v>
@@ -25147,7 +25860,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>43</v>
+        <v>358</v>
       </c>
       <c r="C338">
         <v>614</v>
@@ -25218,7 +25931,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>173</v>
+        <v>359</v>
       </c>
       <c r="C339">
         <v>1047</v>
@@ -25289,7 +26002,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>203</v>
+        <v>360</v>
       </c>
       <c r="C340">
         <v>851</v>
@@ -25360,7 +26073,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>204</v>
+        <v>361</v>
       </c>
       <c r="C341">
         <v>523</v>
@@ -25431,7 +26144,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>205</v>
+        <v>362</v>
       </c>
       <c r="C342">
         <v>875</v>
@@ -25502,7 +26215,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>206</v>
+        <v>363</v>
       </c>
       <c r="C343">
         <v>1205</v>
@@ -25573,7 +26286,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>206</v>
+        <v>364</v>
       </c>
       <c r="C344">
         <v>1077</v>
@@ -25644,7 +26357,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>207</v>
+        <v>365</v>
       </c>
       <c r="C345">
         <v>954</v>
@@ -25715,7 +26428,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>208</v>
+        <v>366</v>
       </c>
       <c r="C346">
         <v>874</v>
@@ -25786,7 +26499,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>209</v>
+        <v>367</v>
       </c>
       <c r="C347">
         <v>1027</v>
@@ -25857,7 +26570,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>210</v>
+        <v>368</v>
       </c>
       <c r="C348">
         <v>1128</v>
@@ -25928,7 +26641,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>211</v>
+        <v>369</v>
       </c>
       <c r="C349">
         <v>1038</v>
@@ -25999,7 +26712,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>211</v>
+        <v>370</v>
       </c>
       <c r="C350">
         <v>626</v>
@@ -26070,7 +26783,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>212</v>
+        <v>371</v>
       </c>
       <c r="C351">
         <v>1181</v>
@@ -26141,7 +26854,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>213</v>
+        <v>372</v>
       </c>
       <c r="C352">
         <v>1197</v>
@@ -26212,7 +26925,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>212</v>
+        <v>371</v>
       </c>
       <c r="C353">
         <v>1161</v>
@@ -26283,7 +26996,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>214</v>
+        <v>373</v>
       </c>
       <c r="C354">
         <v>1059</v>
@@ -26354,7 +27067,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>215</v>
+        <v>374</v>
       </c>
       <c r="C355">
         <v>1174</v>
@@ -26425,7 +27138,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>216</v>
+        <v>375</v>
       </c>
       <c r="C356">
         <v>767</v>
@@ -26496,7 +27209,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>217</v>
+        <v>376</v>
       </c>
       <c r="C357">
         <v>609</v>
@@ -26567,7 +27280,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>218</v>
+        <v>377</v>
       </c>
       <c r="C358">
         <v>679</v>
@@ -26638,7 +27351,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>219</v>
+        <v>378</v>
       </c>
       <c r="C359">
         <v>1232</v>
@@ -26709,7 +27422,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>96</v>
+        <v>379</v>
       </c>
       <c r="C360">
         <v>765</v>
@@ -26780,7 +27493,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>96</v>
+        <v>380</v>
       </c>
       <c r="C361">
         <v>576</v>
@@ -26851,7 +27564,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>87</v>
+        <v>381</v>
       </c>
       <c r="C362">
         <v>1035</v>
@@ -26922,7 +27635,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>220</v>
+        <v>382</v>
       </c>
       <c r="C363">
         <v>676</v>
@@ -26993,7 +27706,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>73</v>
+        <v>383</v>
       </c>
       <c r="C364">
         <v>1100</v>
@@ -27064,7 +27777,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>221</v>
+        <v>384</v>
       </c>
       <c r="C365">
         <v>881</v>
@@ -27135,7 +27848,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>222</v>
+        <v>385</v>
       </c>
       <c r="C366">
         <v>729</v>
@@ -27206,7 +27919,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>223</v>
+        <v>386</v>
       </c>
       <c r="C367">
         <v>675</v>
@@ -27277,7 +27990,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>224</v>
+        <v>387</v>
       </c>
       <c r="C368">
         <v>1189</v>
@@ -27348,7 +28061,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>225</v>
+        <v>388</v>
       </c>
       <c r="C369">
         <v>1087</v>
@@ -27419,7 +28132,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>43</v>
+        <v>389</v>
       </c>
       <c r="C370">
         <v>610</v>
@@ -27490,7 +28203,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>173</v>
+        <v>390</v>
       </c>
       <c r="C371">
         <v>731</v>
@@ -27561,7 +28274,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>226</v>
+        <v>391</v>
       </c>
       <c r="C372">
         <v>803</v>
@@ -27632,7 +28345,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>226</v>
+        <v>392</v>
       </c>
       <c r="C373">
         <v>623</v>
@@ -27703,7 +28416,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>227</v>
+        <v>393</v>
       </c>
       <c r="C374">
         <v>1184</v>
@@ -27774,7 +28487,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>66</v>
+        <v>394</v>
       </c>
       <c r="C375">
         <v>773</v>
@@ -27845,7 +28558,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>67</v>
+        <v>395</v>
       </c>
       <c r="C376">
         <v>765</v>
@@ -27916,7 +28629,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>228</v>
+        <v>396</v>
       </c>
       <c r="C377">
         <v>1065</v>
@@ -27987,7 +28700,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>173</v>
+        <v>397</v>
       </c>
       <c r="C378">
         <v>685</v>
@@ -28058,7 +28771,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>229</v>
+        <v>398</v>
       </c>
       <c r="C379">
         <v>786</v>
@@ -28129,7 +28842,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>230</v>
+        <v>399</v>
       </c>
       <c r="C380">
         <v>1083</v>
@@ -28200,7 +28913,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>231</v>
+        <v>400</v>
       </c>
       <c r="C381">
         <v>1201</v>
@@ -28271,7 +28984,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>11</v>
+        <v>401</v>
       </c>
       <c r="C382">
         <v>815</v>
@@ -28342,7 +29055,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>232</v>
+        <v>402</v>
       </c>
       <c r="C383">
         <v>595</v>
@@ -28413,7 +29126,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>233</v>
+        <v>403</v>
       </c>
       <c r="C384">
         <v>680</v>
@@ -28484,7 +29197,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="s">
-        <v>43</v>
+        <v>404</v>
       </c>
       <c r="C385">
         <v>365</v>
@@ -28555,7 +29268,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="s">
-        <v>234</v>
+        <v>404</v>
       </c>
       <c r="C386">
         <v>831</v>
@@ -28626,7 +29339,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="s">
-        <v>235</v>
+        <v>405</v>
       </c>
       <c r="C387">
         <v>1096</v>
@@ -28697,7 +29410,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="s">
-        <v>236</v>
+        <v>406</v>
       </c>
       <c r="C388">
         <v>969</v>
@@ -28768,7 +29481,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="s">
-        <v>237</v>
+        <v>407</v>
       </c>
       <c r="C389">
         <v>836</v>
@@ -28839,7 +29552,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="s">
-        <v>238</v>
+        <v>408</v>
       </c>
       <c r="C390">
         <v>941</v>
@@ -28910,7 +29623,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="s">
-        <v>238</v>
+        <v>409</v>
       </c>
       <c r="C391">
         <v>683</v>
@@ -28981,7 +29694,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="s">
-        <v>238</v>
+        <v>410</v>
       </c>
       <c r="C392">
         <v>989</v>
@@ -29052,7 +29765,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="s">
-        <v>238</v>
+        <v>411</v>
       </c>
       <c r="C393">
         <v>1002</v>
@@ -29123,7 +29836,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="s">
-        <v>238</v>
+        <v>412</v>
       </c>
       <c r="C394">
         <v>684</v>
@@ -29194,7 +29907,7 @@
         <v>393</v>
       </c>
       <c r="B395" t="s">
-        <v>85</v>
+        <v>412</v>
       </c>
       <c r="C395">
         <v>1243</v>
@@ -29265,7 +29978,7 @@
         <v>394</v>
       </c>
       <c r="B396" t="s">
-        <v>239</v>
+        <v>413</v>
       </c>
       <c r="C396">
         <v>1119</v>
@@ -29336,7 +30049,7 @@
         <v>395</v>
       </c>
       <c r="B397" t="s">
-        <v>240</v>
+        <v>414</v>
       </c>
       <c r="C397">
         <v>1072</v>
@@ -29407,7 +30120,7 @@
         <v>396</v>
       </c>
       <c r="B398" t="s">
-        <v>240</v>
+        <v>415</v>
       </c>
       <c r="C398">
         <v>624</v>
@@ -29478,7 +30191,7 @@
         <v>397</v>
       </c>
       <c r="B399" t="s">
-        <v>85</v>
+        <v>416</v>
       </c>
       <c r="C399">
         <v>577</v>
@@ -29549,7 +30262,7 @@
         <v>398</v>
       </c>
       <c r="B400" t="s">
-        <v>241</v>
+        <v>417</v>
       </c>
       <c r="C400">
         <v>964</v>
@@ -29620,7 +30333,7 @@
         <v>399</v>
       </c>
       <c r="B401" t="s">
-        <v>242</v>
+        <v>418</v>
       </c>
       <c r="C401">
         <v>948</v>
@@ -29691,7 +30404,7 @@
         <v>400</v>
       </c>
       <c r="B402" t="s">
-        <v>242</v>
+        <v>419</v>
       </c>
       <c r="C402">
         <v>521</v>
@@ -29762,7 +30475,7 @@
         <v>401</v>
       </c>
       <c r="B403" t="s">
-        <v>203</v>
+        <v>420</v>
       </c>
       <c r="C403">
         <v>815</v>
@@ -29833,7 +30546,7 @@
         <v>402</v>
       </c>
       <c r="B404" t="s">
-        <v>79</v>
+        <v>421</v>
       </c>
       <c r="C404">
         <v>768</v>
@@ -29904,7 +30617,7 @@
         <v>403</v>
       </c>
       <c r="B405" t="s">
-        <v>80</v>
+        <v>422</v>
       </c>
       <c r="C405">
         <v>622</v>
@@ -29975,7 +30688,7 @@
         <v>404</v>
       </c>
       <c r="B406" t="s">
-        <v>89</v>
+        <v>423</v>
       </c>
       <c r="C406">
         <v>1072</v>
@@ -30046,7 +30759,7 @@
         <v>405</v>
       </c>
       <c r="B407" t="s">
-        <v>90</v>
+        <v>424</v>
       </c>
       <c r="C407">
         <v>1144</v>
@@ -30117,7 +30830,7 @@
         <v>406</v>
       </c>
       <c r="B408" t="s">
-        <v>11</v>
+        <v>425</v>
       </c>
       <c r="C408">
         <v>505</v>
@@ -30188,7 +30901,7 @@
         <v>407</v>
       </c>
       <c r="B409" t="s">
-        <v>177</v>
+        <v>426</v>
       </c>
       <c r="C409">
         <v>1001</v>
@@ -30259,7 +30972,7 @@
         <v>408</v>
       </c>
       <c r="B410" t="s">
-        <v>177</v>
+        <v>427</v>
       </c>
       <c r="C410">
         <v>1048</v>
@@ -30330,7 +31043,7 @@
         <v>409</v>
       </c>
       <c r="B411" t="s">
-        <v>243</v>
+        <v>428</v>
       </c>
       <c r="C411">
         <v>752</v>
@@ -30401,7 +31114,7 @@
         <v>410</v>
       </c>
       <c r="B412" t="s">
-        <v>244</v>
+        <v>429</v>
       </c>
       <c r="C412">
         <v>720</v>
@@ -30472,7 +31185,7 @@
         <v>411</v>
       </c>
       <c r="B413" t="s">
-        <v>245</v>
+        <v>430</v>
       </c>
       <c r="C413">
         <v>485</v>
@@ -30543,7 +31256,7 @@
         <v>412</v>
       </c>
       <c r="B414" t="s">
-        <v>246</v>
+        <v>431</v>
       </c>
       <c r="C414">
         <v>869</v>
@@ -30614,7 +31327,7 @@
         <v>413</v>
       </c>
       <c r="B415" t="s">
-        <v>247</v>
+        <v>432</v>
       </c>
       <c r="C415">
         <v>990</v>
@@ -30685,7 +31398,7 @@
         <v>414</v>
       </c>
       <c r="B416" t="s">
-        <v>248</v>
+        <v>433</v>
       </c>
       <c r="C416">
         <v>650</v>
@@ -30756,7 +31469,7 @@
         <v>415</v>
       </c>
       <c r="B417" t="s">
-        <v>249</v>
+        <v>434</v>
       </c>
       <c r="C417">
         <v>1069</v>
@@ -30827,7 +31540,7 @@
         <v>416</v>
       </c>
       <c r="B418" t="s">
-        <v>250</v>
+        <v>435</v>
       </c>
       <c r="C418">
         <v>1100</v>
@@ -30898,7 +31611,7 @@
         <v>417</v>
       </c>
       <c r="B419" t="s">
-        <v>251</v>
+        <v>436</v>
       </c>
       <c r="C419">
         <v>1058</v>
@@ -30969,7 +31682,7 @@
         <v>418</v>
       </c>
       <c r="B420" t="s">
-        <v>250</v>
+        <v>437</v>
       </c>
       <c r="C420">
         <v>1027</v>
@@ -31040,7 +31753,7 @@
         <v>419</v>
       </c>
       <c r="B421" t="s">
-        <v>250</v>
+        <v>438</v>
       </c>
       <c r="C421">
         <v>1057</v>
@@ -31111,7 +31824,7 @@
         <v>420</v>
       </c>
       <c r="B422" t="s">
-        <v>252</v>
+        <v>439</v>
       </c>
       <c r="C422">
         <v>864</v>
@@ -31182,7 +31895,7 @@
         <v>421</v>
       </c>
       <c r="B423" t="s">
-        <v>253</v>
+        <v>440</v>
       </c>
       <c r="C423">
         <v>1192</v>
@@ -31253,7 +31966,7 @@
         <v>422</v>
       </c>
       <c r="B424" t="s">
-        <v>253</v>
+        <v>441</v>
       </c>
       <c r="C424">
         <v>689</v>
@@ -31324,7 +32037,7 @@
         <v>423</v>
       </c>
       <c r="B425" t="s">
-        <v>254</v>
+        <v>442</v>
       </c>
       <c r="C425">
         <v>1122</v>
@@ -31395,7 +32108,7 @@
         <v>424</v>
       </c>
       <c r="B426" t="s">
-        <v>255</v>
+        <v>443</v>
       </c>
       <c r="C426">
         <v>1221</v>
@@ -31466,7 +32179,7 @@
         <v>425</v>
       </c>
       <c r="B427" t="s">
-        <v>256</v>
+        <v>444</v>
       </c>
       <c r="C427">
         <v>1047</v>
@@ -31537,7 +32250,7 @@
         <v>426</v>
       </c>
       <c r="B428" t="s">
-        <v>254</v>
+        <v>445</v>
       </c>
       <c r="C428">
         <v>1050</v>
@@ -31608,7 +32321,7 @@
         <v>427</v>
       </c>
       <c r="B429" t="s">
-        <v>254</v>
+        <v>446</v>
       </c>
       <c r="C429">
         <v>722</v>
@@ -31679,7 +32392,7 @@
         <v>428</v>
       </c>
       <c r="B430" t="s">
-        <v>254</v>
+        <v>447</v>
       </c>
       <c r="C430">
         <v>586</v>
@@ -31750,7 +32463,7 @@
         <v>429</v>
       </c>
       <c r="B431" t="s">
-        <v>257</v>
+        <v>448</v>
       </c>
       <c r="C431">
         <v>1067</v>
@@ -31821,7 +32534,7 @@
         <v>430</v>
       </c>
       <c r="B432" t="s">
-        <v>258</v>
+        <v>449</v>
       </c>
       <c r="C432">
         <v>1108</v>
@@ -31892,7 +32605,7 @@
         <v>431</v>
       </c>
       <c r="B433" t="s">
-        <v>259</v>
+        <v>450</v>
       </c>
       <c r="C433">
         <v>829</v>
@@ -31963,7 +32676,7 @@
         <v>432</v>
       </c>
       <c r="B434" t="s">
-        <v>260</v>
+        <v>451</v>
       </c>
       <c r="C434">
         <v>994</v>
@@ -32034,7 +32747,7 @@
         <v>433</v>
       </c>
       <c r="B435" t="s">
-        <v>261</v>
+        <v>452</v>
       </c>
       <c r="C435">
         <v>862</v>
@@ -32105,7 +32818,7 @@
         <v>434</v>
       </c>
       <c r="B436" t="s">
-        <v>262</v>
+        <v>453</v>
       </c>
       <c r="C436">
         <v>1038</v>
@@ -32176,7 +32889,7 @@
         <v>435</v>
       </c>
       <c r="B437" t="s">
-        <v>263</v>
+        <v>454</v>
       </c>
       <c r="C437">
         <v>1110</v>
@@ -32247,7 +32960,7 @@
         <v>436</v>
       </c>
       <c r="B438" t="s">
-        <v>263</v>
+        <v>455</v>
       </c>
       <c r="C438">
         <v>1187</v>
@@ -32318,7 +33031,7 @@
         <v>437</v>
       </c>
       <c r="B439" t="s">
-        <v>264</v>
+        <v>456</v>
       </c>
       <c r="C439">
         <v>1221</v>
@@ -32389,7 +33102,7 @@
         <v>438</v>
       </c>
       <c r="B440" t="s">
-        <v>265</v>
+        <v>457</v>
       </c>
       <c r="C440">
         <v>1072</v>
@@ -32460,7 +33173,7 @@
         <v>439</v>
       </c>
       <c r="B441" t="s">
-        <v>266</v>
+        <v>458</v>
       </c>
       <c r="C441">
         <v>952</v>
@@ -32531,7 +33244,7 @@
         <v>440</v>
       </c>
       <c r="B442" t="s">
-        <v>267</v>
+        <v>459</v>
       </c>
       <c r="C442">
         <v>660</v>
@@ -32602,7 +33315,7 @@
         <v>441</v>
       </c>
       <c r="B443" t="s">
-        <v>268</v>
+        <v>460</v>
       </c>
       <c r="C443">
         <v>688</v>
@@ -32673,7 +33386,7 @@
         <v>442</v>
       </c>
       <c r="B444" t="s">
-        <v>269</v>
+        <v>461</v>
       </c>
       <c r="C444">
         <v>639</v>
@@ -32744,7 +33457,7 @@
         <v>443</v>
       </c>
       <c r="B445" t="s">
-        <v>270</v>
+        <v>462</v>
       </c>
       <c r="C445">
         <v>927</v>
@@ -32815,7 +33528,7 @@
         <v>444</v>
       </c>
       <c r="B446" t="s">
-        <v>271</v>
+        <v>463</v>
       </c>
       <c r="C446">
         <v>982</v>
@@ -32886,7 +33599,7 @@
         <v>445</v>
       </c>
       <c r="B447" t="s">
-        <v>270</v>
+        <v>464</v>
       </c>
       <c r="C447">
         <v>1228</v>
@@ -32957,7 +33670,7 @@
         <v>446</v>
       </c>
       <c r="B448" t="s">
-        <v>270</v>
+        <v>465</v>
       </c>
       <c r="C448">
         <v>836</v>
@@ -33028,7 +33741,7 @@
         <v>447</v>
       </c>
       <c r="B449" t="s">
-        <v>272</v>
+        <v>466</v>
       </c>
       <c r="C449">
         <v>623</v>
@@ -33099,7 +33812,7 @@
         <v>448</v>
       </c>
       <c r="B450" t="s">
-        <v>273</v>
+        <v>467</v>
       </c>
       <c r="C450">
         <v>657</v>
@@ -33170,7 +33883,7 @@
         <v>449</v>
       </c>
       <c r="B451" t="s">
-        <v>274</v>
+        <v>468</v>
       </c>
       <c r="C451">
         <v>1025</v>
@@ -33241,7 +33954,7 @@
         <v>450</v>
       </c>
       <c r="B452" t="s">
-        <v>274</v>
+        <v>469</v>
       </c>
       <c r="C452">
         <v>1055</v>
@@ -33312,7 +34025,7 @@
         <v>451</v>
       </c>
       <c r="B453" t="s">
-        <v>274</v>
+        <v>470</v>
       </c>
       <c r="C453">
         <v>1010</v>
@@ -33383,7 +34096,7 @@
         <v>452</v>
       </c>
       <c r="B454" t="s">
-        <v>275</v>
+        <v>471</v>
       </c>
       <c r="C454">
         <v>1227</v>
@@ -33454,7 +34167,7 @@
         <v>453</v>
       </c>
       <c r="B455" t="s">
-        <v>276</v>
+        <v>472</v>
       </c>
       <c r="C455">
         <v>1065</v>
@@ -33525,7 +34238,7 @@
         <v>454</v>
       </c>
       <c r="B456" t="s">
-        <v>277</v>
+        <v>473</v>
       </c>
       <c r="C456">
         <v>1069</v>
@@ -33596,7 +34309,7 @@
         <v>455</v>
       </c>
       <c r="B457" t="s">
-        <v>278</v>
+        <v>474</v>
       </c>
       <c r="C457">
         <v>776</v>
@@ -33667,7 +34380,7 @@
         <v>456</v>
       </c>
       <c r="B458" t="s">
-        <v>279</v>
+        <v>475</v>
       </c>
       <c r="C458">
         <v>994</v>
@@ -33738,7 +34451,7 @@
         <v>457</v>
       </c>
       <c r="B459" t="s">
-        <v>165</v>
+        <v>476</v>
       </c>
       <c r="C459">
         <v>839</v>
@@ -33809,7 +34522,7 @@
         <v>458</v>
       </c>
       <c r="B460" t="s">
-        <v>165</v>
+        <v>477</v>
       </c>
       <c r="C460">
         <v>886</v>
@@ -33880,7 +34593,7 @@
         <v>459</v>
       </c>
       <c r="B461" t="s">
-        <v>165</v>
+        <v>478</v>
       </c>
       <c r="C461">
         <v>940</v>
@@ -33951,7 +34664,7 @@
         <v>460</v>
       </c>
       <c r="B462" t="s">
-        <v>235</v>
+        <v>479</v>
       </c>
       <c r="C462">
         <v>932</v>
@@ -34022,7 +34735,7 @@
         <v>461</v>
       </c>
       <c r="B463" t="s">
-        <v>280</v>
+        <v>480</v>
       </c>
       <c r="C463">
         <v>808</v>
@@ -34093,7 +34806,7 @@
         <v>462</v>
       </c>
       <c r="B464" t="s">
-        <v>235</v>
+        <v>481</v>
       </c>
       <c r="C464">
         <v>752</v>
@@ -34164,7 +34877,7 @@
         <v>463</v>
       </c>
       <c r="B465" t="s">
-        <v>281</v>
+        <v>482</v>
       </c>
       <c r="C465">
         <v>941</v>
@@ -34235,7 +34948,7 @@
         <v>464</v>
       </c>
       <c r="B466" t="s">
-        <v>282</v>
+        <v>483</v>
       </c>
       <c r="C466">
         <v>671</v>
@@ -34306,7 +35019,7 @@
         <v>465</v>
       </c>
       <c r="B467" t="s">
-        <v>177</v>
+        <v>484</v>
       </c>
       <c r="C467">
         <v>1053</v>
@@ -34377,7 +35090,7 @@
         <v>466</v>
       </c>
       <c r="B468" t="s">
-        <v>177</v>
+        <v>485</v>
       </c>
       <c r="C468">
         <v>934</v>
@@ -34448,7 +35161,7 @@
         <v>467</v>
       </c>
       <c r="B469" t="s">
-        <v>281</v>
+        <v>486</v>
       </c>
       <c r="C469">
         <v>680</v>
@@ -34519,7 +35232,7 @@
         <v>468</v>
       </c>
       <c r="B470" t="s">
-        <v>282</v>
+        <v>487</v>
       </c>
       <c r="C470">
         <v>635</v>
@@ -34590,7 +35303,7 @@
         <v>469</v>
       </c>
       <c r="B471" t="s">
-        <v>283</v>
+        <v>488</v>
       </c>
       <c r="C471">
         <v>708</v>
@@ -34661,7 +35374,7 @@
         <v>470</v>
       </c>
       <c r="B472" t="s">
-        <v>284</v>
+        <v>489</v>
       </c>
       <c r="C472">
         <v>638</v>
@@ -34732,7 +35445,7 @@
         <v>471</v>
       </c>
       <c r="B473" t="s">
-        <v>285</v>
+        <v>490</v>
       </c>
       <c r="C473">
         <v>1243</v>
@@ -34803,7 +35516,7 @@
         <v>472</v>
       </c>
       <c r="B474" t="s">
-        <v>286</v>
+        <v>491</v>
       </c>
       <c r="C474">
         <v>651</v>
@@ -34874,7 +35587,7 @@
         <v>473</v>
       </c>
       <c r="B475" t="s">
-        <v>287</v>
+        <v>492</v>
       </c>
       <c r="C475">
         <v>604</v>
@@ -34945,7 +35658,7 @@
         <v>474</v>
       </c>
       <c r="B476" t="s">
-        <v>66</v>
+        <v>493</v>
       </c>
       <c r="C476">
         <v>1198</v>
@@ -35016,7 +35729,7 @@
         <v>475</v>
       </c>
       <c r="B477" t="s">
-        <v>67</v>
+        <v>494</v>
       </c>
       <c r="C477">
         <v>672</v>
@@ -35087,7 +35800,7 @@
         <v>476</v>
       </c>
       <c r="B478" t="s">
-        <v>288</v>
+        <v>495</v>
       </c>
       <c r="C478">
         <v>588</v>
@@ -35158,7 +35871,7 @@
         <v>477</v>
       </c>
       <c r="B479" t="s">
-        <v>289</v>
+        <v>496</v>
       </c>
       <c r="C479">
         <v>1166</v>
